--- a/LP-Pair-Rankings.xlsx
+++ b/LP-Pair-Rankings.xlsx
@@ -15,7 +15,7 @@
     <sheet name="All Supported" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier 1'!$A$4:$U$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tier 1'!$A$4:$U$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tier 2'!$A$4:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Tier 3'!$A$4:$U$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Correlated Pairs'!$A$4:$U$21</definedName>
@@ -212,8 +212,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TTier1" displayName="TTier1" ref="A4:U44" headerRowCount="1">
-  <autoFilter ref="A4:U44"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TTier1" displayName="TTier1" ref="A4:U45" headerRowCount="1">
+  <autoFilter ref="A4:U45"/>
   <tableColumns count="21">
     <tableColumn id="1" name="Rank"/>
     <tableColumn id="2" name="Pair"/>
@@ -777,7 +777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U44"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -952,31 +952,31 @@
         <v>444029.22</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>646286.55</v>
+        <v>645888.45</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>1.45550454990327</v>
+        <v>1.454607987285161</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="M5" s="10" t="n">
         <v>6.53</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>451.5702866074895</v>
+        <v>451.2921280552213</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -1034,34 +1034,34 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>464541.32</v>
+        <v>464540.71</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>1393323.29</v>
+        <v>1388167.72</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2.999352759405773</v>
+        <v>2.988258488690905</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9759036144578314</v>
       </c>
       <c r="L6" s="10" t="n">
         <v>-0.96</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>-3.24</v>
+        <v>-3.23</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>-2.28</v>
+        <v>-2.54</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>279.1647580816922</v>
+        <v>278.132158834906</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -1119,13 +1119,13 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>540221.3</v>
+        <v>540093.92</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>357253.56</v>
+        <v>357384.68</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>0.6613096521740257</v>
+        <v>0.6617083932364948</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>26</v>
@@ -1137,16 +1137,16 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>205.1713195869914</v>
+        <v>205.2950290016225</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -1204,34 +1204,34 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>276548</v>
+        <v>277089.22</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>176664.49</v>
+        <v>176665.09</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>0.6388203494510898</v>
+        <v>0.6375747493893844</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.18</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-3.32</v>
+        <v>-3.13</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>198.1940134172006</v>
+        <v>197.8075659980566</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -1377,10 +1377,10 @@
         <v>681068.66</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>412199.7</v>
+        <v>411902.22</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>0.605224882906813</v>
+        <v>0.6047880987505723</v>
       </c>
       <c r="I10" s="6" t="n">
         <v>11</v>
@@ -1395,13 +1395,13 @@
         <v>1.25</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>6.59</v>
+        <v>6.24</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>187.7710199218387</v>
+        <v>187.635507637365</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -1459,34 +1459,34 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>250818.54</v>
+        <v>250811.61</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>493179.62</v>
+        <v>493112.79</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1.966280562832396</v>
+        <v>1.966068436784087</v>
       </c>
       <c r="I11" s="6" t="n">
         <v>39</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.3277310924369748</v>
+        <v>0.3223140495867768</v>
       </c>
       <c r="L11" s="10" t="n">
         <v>-1</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="N11" s="10" t="n">
         <v>-2.49</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>183.0115633856253</v>
+        <v>182.9918197536789</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -1606,7 +1606,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -1629,34 +1629,34 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>466053.49</v>
+        <v>466196.16</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>802430.85</v>
+        <v>803978.08</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1.72175698115682</v>
+        <v>1.72454891091338</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>60</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-0.34</v>
+        <v>-0.25</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>7.22</v>
+        <v>7.32</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>160.252531021171</v>
+        <v>160.5123898832629</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -1680,7 +1680,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -1811,16 +1811,16 @@
         <v>55</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.8208955223880597</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>-2.08</v>
+        <v>-2.17</v>
       </c>
       <c r="N15" s="10" t="n">
         <v>2.16</v>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -1896,16 +1896,16 @@
         <v>228</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.4653061224489796</v>
+        <v>0.474012474012474</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-1.51</v>
+        <v>-1.33</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="N16" s="10" t="n">
         <v>13.42</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -1969,34 +1969,34 @@
         </is>
       </c>
       <c r="F17" s="7" t="n">
-        <v>1344800.21</v>
+        <v>1344802.18</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>1812850.36</v>
+        <v>1810613.31</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>1.34804437604899</v>
+        <v>1.346378922437499</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>171</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8654970760233918</v>
       </c>
       <c r="L17" s="10" t="n">
         <v>-0.33</v>
       </c>
       <c r="M17" s="10" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="N17" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="O17" s="10" t="n">
-        <v>125.4692303007597</v>
+        <v>125.3142182058702</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -2054,34 +2054,34 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>550552.28</v>
+        <v>550934.48</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>706242.49</v>
+        <v>711573.35</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1.282789147653698</v>
+        <v>1.291575270438692</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J18" s="6" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.5585106382978723</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>-1.39</v>
+        <v>-1.03</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>-2.85</v>
+        <v>-2.71</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>-2.13</v>
+        <v>-1.96</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>119.3955999178679</v>
+        <v>120.2133682960812</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -2201,11 +2201,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>WALLET / WETH</t>
+          <t>WETH / Index</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -2215,7 +2215,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>0x9501A20Bedb8beA0798FE5D4c411f5e270965D49</t>
+          <t>0xD29893fFac8b29eC4Db2cfE0CDB3FE1377c028Ff</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2224,43 +2224,43 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>2278849.27</v>
+        <v>959150.86</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>696911.62</v>
+        <v>335058.94</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>0.3058173391169483</v>
+        <v>0.3493287176951497</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>5.89</v>
+        <v>-0.02</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>6.48</v>
+        <v>2.88</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>24.52</v>
+        <v>2.26</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>94.8798294610332</v>
+        <v>108.3792346649202</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 43.33% / 12h</t>
+          <t>Aggressive 49.2% / 8h</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -2286,71 +2286,71 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>WETH / NVDA</t>
+          <t>WALLET / WETH</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0xC0Be1cb0f674D9737C72B2A63fC542361185b807</t>
+          <t>0x9501A20Bedb8beA0798FE5D4c411f5e270965D49</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>meme</t>
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>304250.64</v>
+        <v>2282878.99</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>281928.27</v>
+        <v>675280.51</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>0.9266316415965469</v>
+        <v>0.2958021484967103</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.9</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-0.73</v>
+        <v>6.04</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>-0.88</v>
+        <v>6.48</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>0.7</v>
+        <v>24.25</v>
       </c>
       <c r="O21" s="10" t="n">
-        <v>86.24624004159861</v>
+        <v>91.77261657110436</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 2.43% / 2h</t>
+          <t>Aggressive 43.33% / 12h</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S21" s="6" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -2371,11 +2371,11 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>USDG / MSFT</t>
+          <t>WETH / NVDA</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>0xeb60bcd1d920ad6e102690ccfc6fb488899e1510</t>
+          <t>0xC0Be1cb0f674D9737C72B2A63fC542361185b807</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2394,38 +2394,38 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>740627.9300000001</v>
+        <v>304845.23</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>679266.0699999999</v>
+        <v>281928.8</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>0.9171488712287692</v>
+        <v>0.9248260174515442</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>342</v>
+        <v>56</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>368</v>
+        <v>86</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.9293478260869565</v>
+        <v>0.6511627906976745</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>-0.06</v>
+        <v>-0.87</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>3.6</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>4.14</v>
+        <v>0.9</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>85.36363118961769</v>
+        <v>86.07818157430248</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 2.43% / 2h</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -2456,11 +2456,11 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>WETH / PONS</t>
+          <t>USDG / MSFT</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -2470,57 +2470,57 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>0xEd50bDeeA8aDC232f159486192a4157281D722ff</t>
+          <t>0xeb60bcd1d920ad6e102690ccfc6fb488899e1510</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>meme</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>5996224.34</v>
+        <v>740629.83</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>5341727.21</v>
+        <v>679330.22</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>0.8908484584817919</v>
+        <v>0.9172331338585161</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>240</v>
+        <v>343</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>339</v>
+        <v>367</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.9346049046321526</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-0.53</v>
+        <v>-0.06</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>-1.82</v>
+        <v>3.6</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>3.22</v>
+        <v>4.14</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>82.91572027319279</v>
+        <v>85.37147393388138</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 30.21% / 8h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S23" s="6" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -2541,11 +2541,11 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>WETH / QQQ</t>
+          <t>WETH / PONS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -2555,57 +2555,57 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>0xA40D00a55d43bA2d188039DCF88bD68f4F133E78</t>
+          <t>0xEd50bDeeA8aDC232f159486192a4157281D722ff</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>meme</t>
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>301585.79</v>
+        <v>6001307.55</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>268451.79</v>
+        <v>5348113.7</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>0.8901340809193961</v>
+        <v>0.8911580777092486</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>14</v>
+        <v>261</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>39</v>
+        <v>312</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.358974358974359</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>-0.47</v>
+        <v>-0.27</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>-0.46</v>
+        <v>-1.7</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>0.47</v>
+        <v>3.39</v>
       </c>
       <c r="O24" s="10" t="n">
-        <v>82.8492295815728</v>
+        <v>82.94453808278833</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 12.75% / 2h</t>
+          <t>Aggressive 30.21% / 8h</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S24" s="6" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -2626,71 +2626,71 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>WETH / CHUMP</t>
+          <t>WETH / QQQ</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>0x714442e9A611f8561A7dF108D6d925132937cFb8</t>
+          <t>0xA40D00a55d43bA2d188039DCF88bD68f4F133E78</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>meme</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F25" s="7" t="n">
-        <v>1116959.31</v>
+        <v>301585.79</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>267586.13</v>
+        <v>268451.79</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>0.2395665872555375</v>
+        <v>0.8901340809193961</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>101</v>
+        <v>14</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8347107438016529</v>
+        <v>0.358974358974359</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>-0.74</v>
+        <v>-0.47</v>
       </c>
       <c r="M25" s="10" t="n">
-        <v>-1.93</v>
+        <v>-0.46</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>-3.48</v>
+        <v>0.47</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>74.3255336960305</v>
+        <v>82.8492295815728</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 122.55% / 12h</t>
+          <t>Aggressive 12.75% / 2h</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S25" s="6" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -2711,11 +2711,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>DJT / USDG</t>
+          <t>WETH / CHUMP</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -2725,57 +2725,57 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>0x31a89afd92F9397465649AD03226c52292fc1ae5</t>
+          <t>0x714442e9A611f8561A7dF108D6d925132937cFb8</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>meme</t>
         </is>
       </c>
       <c r="F26" s="7" t="n">
-        <v>393856.93</v>
+        <v>1116812.62</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>86424.33</v>
+        <v>267590.98</v>
       </c>
       <c r="H26" s="8" t="n">
-        <v>0.219430771473286</v>
+        <v>0.2396023963267893</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>7</v>
+        <v>99</v>
       </c>
       <c r="J26" s="6" t="n">
-        <v>5</v>
+        <v>122</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.8114754098360656</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>0</v>
+        <v>-0.77</v>
       </c>
       <c r="M26" s="10" t="n">
-        <v>0.46</v>
+        <v>-1.99</v>
       </c>
       <c r="N26" s="10" t="n">
-        <v>1.16</v>
+        <v>-3.51</v>
       </c>
       <c r="O26" s="10" t="n">
-        <v>68.07839684958698</v>
+        <v>74.33664346038638</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 12.75% / 2h</t>
+          <t>Aggressive 122.55% / 12h</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S26" s="6" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -2796,66 +2796,66 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>WETH / USDG</t>
+          <t>DJT / USDG</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>0x52e65B17fB6E5BA00Ed806f37Afcd2DaA50271Ca</t>
+          <t>0x31a89afd92F9397465649AD03226c52292fc1ae5</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>bluechip</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F27" s="7" t="n">
-        <v>19009107.46</v>
+        <v>393856.93</v>
       </c>
       <c r="G27" s="7" t="n">
-        <v>400309023.8</v>
+        <v>86420.66</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>21.05880166348431</v>
+        <v>0.2194214533688667</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>13680</v>
+        <v>7</v>
       </c>
       <c r="J27" s="6" t="n">
-        <v>13026</v>
+        <v>5</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.9521929824561404</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L27" s="10" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="M27" s="10" t="n">
-        <v>0.06</v>
+        <v>0.46</v>
       </c>
       <c r="N27" s="10" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="O27" s="10" t="n">
-        <v>65.33493216096007</v>
+        <v>68.0755059076909</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 5% / 1h</t>
+          <t>Aggressive 12.75% / 2h</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -2881,7 +2881,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>0x69BfaF19C9f377BB306a89aEd9F6B07e2c1a8d9a</t>
+          <t>0x52e65B17fB6E5BA00Ed806f37Afcd2DaA50271Ca</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2904,34 +2904,34 @@
         </is>
       </c>
       <c r="F28" s="7" t="n">
-        <v>4706469.87</v>
+        <v>19007528.26</v>
       </c>
       <c r="G28" s="7" t="n">
-        <v>19510297.65</v>
+        <v>400093412.34</v>
       </c>
       <c r="H28" s="8" t="n">
-        <v>4.145420705731619</v>
+        <v>21.04920781214716</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1652</v>
+        <v>13657</v>
       </c>
       <c r="J28" s="6" t="n">
-        <v>1509</v>
+        <v>13010</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.9134382566585957</v>
+        <v>0.9526250274584462</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="M28" s="10" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="N28" s="10" t="n">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="O28" s="10" t="n">
-        <v>64.30583869766173</v>
+        <v>65.30516723718657</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -2966,7 +2966,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>0xa9188730Fe85Be88ad499D7d52B099e800fB0334</t>
+          <t>0x69BfaF19C9f377BB306a89aEd9F6B07e2c1a8d9a</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -2989,34 +2989,34 @@
         </is>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1551729.91</v>
+        <v>4706340.24</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>1067033.81</v>
+        <v>19507603.76</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>0.687641453015493</v>
+        <v>4.14496249000476</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>76</v>
+        <v>1652</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>103</v>
+        <v>1512</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.7378640776699029</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="L29" s="10" t="n">
-        <v>-0.22</v>
+        <v>-0.06</v>
       </c>
       <c r="M29" s="10" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>64.00222823941701</v>
+        <v>64.29873062619885</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -3051,11 +3051,11 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>WETH / COIN</t>
+          <t>WETH / USDG</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -3065,52 +3065,52 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>0x6707aeAc7D0e519B083219d27BB427364363183A</t>
+          <t>0xa9188730Fe85Be88ad499D7d52B099e800fB0334</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>bluechip</t>
         </is>
       </c>
       <c r="F30" s="7" t="n">
-        <v>581991.35</v>
+        <v>1552229.25</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>395572.92</v>
+        <v>1067033.81</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.6796886586029156</v>
+        <v>0.6874202441424165</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="J30" s="6" t="n">
-        <v>53</v>
+        <v>103</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.3584905660377358</v>
+        <v>0.7378640776699029</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>-0.47</v>
+        <v>-0.22</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>-2.16</v>
+        <v>-0.06</v>
       </c>
       <c r="N30" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>1.22</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>63.26202189946638</v>
+        <v>63.98163922355541</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 12.7% / 2h</t>
+          <t>Aggressive 5% / 1h</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -3136,21 +3136,21 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>WETH / SPCX</t>
+          <t>WETH / COIN</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>0xC3c9F0171490Ef0F4536fe493F3b0EbB5ee0CB5e</t>
+          <t>0x6707aeAc7D0e519B083219d27BB427364363183A</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
@@ -3159,38 +3159,38 @@
         </is>
       </c>
       <c r="F31" s="7" t="n">
-        <v>998463.46</v>
+        <v>581991.35</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>3729429.27</v>
+        <v>395572.92</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>3.735168505815927</v>
+        <v>0.6796886586029156</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>384</v>
+        <v>19</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>407</v>
+        <v>52</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.9434889434889435</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="L31" s="10" t="n">
-        <v>-1.09</v>
+        <v>-0.8</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>-1.42</v>
+        <v>-2.16</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-0.25</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>57.94180144646957</v>
+        <v>63.26202189946638</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 17.35% / 2h</t>
+          <t>Aggressive 12.7% / 2h</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -3221,11 +3221,11 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>SPCX / USDG</t>
+          <t>WETH / SPCX</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -3235,7 +3235,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>0xc61284332117c3FB23A2A56cceFFD07F7aF60029</t>
+          <t>0xC3c9F0171490Ef0F4536fe493F3b0EbB5ee0CB5e</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -3244,43 +3244,43 @@
         </is>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2536305.53</v>
+        <v>998492.49</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>9398407.98</v>
+        <v>3723276.88</v>
       </c>
       <c r="H32" s="8" t="n">
-        <v>3.705550403464208</v>
+        <v>3.728898231372777</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>319</v>
+        <v>386</v>
       </c>
       <c r="J32" s="6" t="n">
-        <v>444</v>
+        <v>403</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.7184684684684685</v>
+        <v>0.9578163771712159</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>-0.82</v>
+        <v>-1.05</v>
       </c>
       <c r="M32" s="10" t="n">
-        <v>-1.56</v>
+        <v>-1.57</v>
       </c>
       <c r="N32" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="O32" s="10" t="n">
-        <v>57.48235063373852</v>
+        <v>57.8445338141702</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 17.35% / 2h</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3295,7 +3295,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -3306,21 +3306,21 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>AMC / USDG</t>
+          <t>SPCX / USDG</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>0xaA34feA710a1A737840329051D81D3B0B7C564d5</t>
+          <t>0xc61284332117c3FB23A2A56cceFFD07F7aF60029</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -3329,43 +3329,43 @@
         </is>
       </c>
       <c r="F33" s="7" t="n">
-        <v>479211.98</v>
+        <v>2536636.13</v>
       </c>
       <c r="G33" s="7" t="n">
-        <v>291057.32</v>
+        <v>9380693.859999999</v>
       </c>
       <c r="H33" s="8" t="n">
-        <v>0.6073665353691701</v>
+        <v>3.6980841473704</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>23</v>
+        <v>323</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>17</v>
+        <v>444</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7274774774774775</v>
       </c>
       <c r="L33" s="10" t="n">
-        <v>-0.29</v>
+        <v>-0.79</v>
       </c>
       <c r="M33" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.54</v>
       </c>
       <c r="N33" s="10" t="n">
-        <v>4.47</v>
+        <v>0.06</v>
       </c>
       <c r="O33" s="10" t="n">
-        <v>56.5306402794855</v>
+        <v>57.36653033608332</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 24.1% / 2h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -3391,21 +3391,21 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>RDDT / USDG</t>
+          <t>AMC / USDG</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>0xa8744E76aED23B05F0126335E7BD38f7935D19fe</t>
+          <t>0xaA34feA710a1A737840329051D81D3B0B7C564d5</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -3414,38 +3414,38 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>1132694.64</v>
+        <v>479211.98</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>205181.46</v>
+        <v>289567.53</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>0.1811445492493899</v>
+        <v>0.6042577024055201</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.375</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>-0.17</v>
+        <v>-0.33</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>0.61</v>
+        <v>-1.42</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>0.92</v>
+        <v>4.47</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>56.20009640462323</v>
+        <v>56.24128565139378</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 24.1% / 2h</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3476,21 +3476,21 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>USDG / AAPL</t>
+          <t>RDDT / USDG</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>0xAae0d815EE56e4092a5E5C2911E676Fea50B2d6D</t>
+          <t>0xa8744E76aED23B05F0126335E7BD38f7935D19fe</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -3499,43 +3499,43 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>474482.4</v>
+        <v>1132694.94</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>1609952.96</v>
+        <v>205184.46</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>3.393072029647464</v>
+        <v>0.1811471498230583</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>122</v>
+        <v>10</v>
       </c>
       <c r="J35" s="6" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.7459016393442623</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>0.36</v>
+        <v>-0.17</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>0.32</v>
+        <v>0.61</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>0.29</v>
+        <v>0.92</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>52.63502985990629</v>
+        <v>56.20090323260383</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 8.33% / 2h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3561,21 +3561,21 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="n">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>USDG / MU</t>
+          <t>USDG / AAPL</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>0xd057B1Bc54917855BBee58eAd58647f47caB35E5</t>
+          <t>0xAae0d815EE56e4092a5E5C2911E676Fea50B2d6D</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -3584,38 +3584,38 @@
         </is>
       </c>
       <c r="F36" s="7" t="n">
-        <v>855414.74</v>
+        <v>474488.54</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>410578.74</v>
+        <v>1608835.49</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.4799762276717373</v>
+        <v>3.390673018151292</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="J36" s="6" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.6538461538461539</v>
+        <v>0.7459016393442623</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>-0.45</v>
+        <v>0.36</v>
       </c>
       <c r="M36" s="10" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.32</v>
       </c>
       <c r="N36" s="10" t="n">
-        <v>2.79</v>
+        <v>0.3</v>
       </c>
       <c r="O36" s="10" t="n">
-        <v>44.67378739054696</v>
+        <v>52.59781519407192</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 27.12% / 2h</t>
+          <t>Aggressive 8.33% / 2h</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
@@ -3635,7 +3635,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3646,21 +3646,21 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="n">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>USDG / LLY</t>
+          <t>USDG / MU</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>0xF212D02146a897F5F686E9d629F6A73da534324a</t>
+          <t>0xd057B1Bc54917855BBee58eAd58647f47caB35E5</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -3669,38 +3669,38 @@
         </is>
       </c>
       <c r="F37" s="7" t="n">
-        <v>329924.4</v>
+        <v>855414.74</v>
       </c>
       <c r="G37" s="7" t="n">
-        <v>925105.77</v>
+        <v>410578.74</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>2.803993187530234</v>
+        <v>0.4799762276717373</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.92</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="L37" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.45</v>
       </c>
       <c r="M37" s="10" t="n">
-        <v>-1.84</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N37" s="10" t="n">
-        <v>-2.31</v>
+        <v>2.79</v>
       </c>
       <c r="O37" s="10" t="n">
-        <v>43.49694432156275</v>
+        <v>44.67378739054696</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 8.33% / 2h</t>
+          <t>Aggressive 27.12% / 2h</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3731,21 +3731,21 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>AMZN / USDG</t>
+          <t>USDG / LLY</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>0x8ac92da74ab5f3b1d024dc1943ad7e15dc4179ef</t>
+          <t>0xF212D02146a897F5F686E9d629F6A73da534324a</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -3754,38 +3754,38 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>830409.27</v>
+        <v>330071.28</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>381636.31</v>
+        <v>928580.63</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.4595761677853138</v>
+        <v>2.813273029995218</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.3875</v>
+        <v>0.98</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.76</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>-0.71</v>
+        <v>-1.77</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>0.64</v>
+        <v>-2.22</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>42.7750518166181</v>
+        <v>43.64089787780082</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 8.33% / 2h</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3816,71 +3816,71 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>WETH / PIPEDOG</t>
+          <t>AMZN / USDG</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>0xB7f10f74B39291b9290b779978e19A7637C742D6</t>
+          <t>0x8ac92da74ab5f3b1d024dc1943ad7e15dc4179ef</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>meme</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>8351126</v>
+        <v>830409.26</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>1143590.73</v>
+        <v>381639.59</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.1369385074539649</v>
+        <v>0.4595801231792623</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>-0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.71</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>-7.31</v>
+        <v>0.64</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>42.48517193759261</v>
+        <v>42.77541996490983</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 37.71% / 12h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S39" s="6" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -3901,71 +3901,71 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>GOOGL / USDG</t>
+          <t>WETH / PIPEDOG</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>0x34D0dC122CF9A8Eb296fC5e0D3A233625D7d19b7</t>
+          <t>0xB7f10f74B39291b9290b779978e19A7637C742D6</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>meme</t>
         </is>
       </c>
       <c r="F40" s="7" t="n">
-        <v>962972.14</v>
+        <v>8351126</v>
       </c>
       <c r="G40" s="7" t="n">
-        <v>2599450.63</v>
+        <v>1141092.91</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>2.699403775066639</v>
+        <v>0.1366394076679001</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>236</v>
+        <v>21</v>
       </c>
       <c r="J40" s="6" t="n">
-        <v>275</v>
+        <v>14</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.8581818181818182</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L40" s="10" t="n">
         <v>-0.17</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>0.15</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N40" s="10" t="n">
-        <v>1.26</v>
+        <v>-7.23</v>
       </c>
       <c r="O40" s="10" t="n">
-        <v>41.87450106072123</v>
+        <v>42.39237622896601</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 2.02% / 2h</t>
+          <t>Aggressive 37.71% / 12h</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S40" s="6" t="inlineStr">
@@ -3975,7 +3975,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -3986,11 +3986,11 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>SPY / USDG</t>
+          <t>GOOGL / USDG</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>0xa7Bb1AC63BBaB0C44316E6c8C455213441689167</t>
+          <t>0x34D0dC122CF9A8Eb296fC5e0D3A233625D7d19b7</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -4009,34 +4009,34 @@
         </is>
       </c>
       <c r="F41" s="7" t="n">
-        <v>363260.97</v>
+        <v>962491.15</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>562407.62</v>
+        <v>2603747.91</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>1.54821923203035</v>
+        <v>2.705217507714227</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>48</v>
+        <v>236</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8166089965397924</v>
       </c>
       <c r="L41" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.27</v>
       </c>
       <c r="M41" s="10" t="n">
-        <v>-0.22</v>
+        <v>0.05</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>0.41</v>
+        <v>1.22</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>24.01675083687081</v>
+        <v>41.96468658841695</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -4071,11 +4071,11 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>USDG / QQQ</t>
+          <t>SPY / USDG</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>0xD60A5d14dB690B7Afad71F76B108071D7175597d</t>
+          <t>0xa7Bb1AC63BBaB0C44316E6c8C455213441689167</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -4094,43 +4094,43 @@
         </is>
       </c>
       <c r="F42" s="7" t="n">
-        <v>1344800.21</v>
+        <v>363260.97</v>
       </c>
       <c r="G42" s="7" t="n">
-        <v>1812850.36</v>
+        <v>560353.84</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>1.34804437604899</v>
+        <v>1.542565500499544</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>147</v>
+        <v>48</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>171</v>
+        <v>58</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>-0.33</v>
+        <v>-0.2</v>
       </c>
       <c r="M42" s="10" t="n">
-        <v>-0.42</v>
+        <v>-0.22</v>
       </c>
       <c r="N42" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.43</v>
       </c>
       <c r="O42" s="10" t="n">
-        <v>20.91153838345995</v>
+        <v>23.92904732649918</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 2.02% / 2h</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4156,11 +4156,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>WETH / NVDA</t>
+          <t>USDG / QQQ</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>0xC0Be1cb0f674D9737C72B2A63fC542361185b807</t>
+          <t>0xD60A5d14dB690B7Afad71F76B108071D7175597d</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
@@ -4179,43 +4179,43 @@
         </is>
       </c>
       <c r="F43" s="7" t="n">
-        <v>304250.64</v>
+        <v>1344802.18</v>
       </c>
       <c r="G43" s="7" t="n">
-        <v>281928.27</v>
+        <v>1810613.31</v>
       </c>
       <c r="H43" s="8" t="n">
-        <v>0.9266316415965469</v>
+        <v>1.346378922437499</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>56</v>
+        <v>148</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>86</v>
+        <v>171</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.6511627906976745</v>
+        <v>0.8654970760233918</v>
       </c>
       <c r="L43" s="10" t="n">
-        <v>-0.73</v>
+        <v>-0.33</v>
       </c>
       <c r="M43" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.43</v>
       </c>
       <c r="N43" s="10" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="O43" s="10" t="n">
-        <v>14.37437334026643</v>
+        <v>20.88570303431171</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 2.43% / 2h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4230,7 +4230,7 @@
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -4241,96 +4241,181 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
+        <v>144</v>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>WETH / NVDA</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>0xC0Be1cb0f674D9737C72B2A63fC542361185b807</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>stocks</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>304845.23</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>281928.8</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0.9248260174515442</v>
+      </c>
+      <c r="I44" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="J44" s="6" t="n">
+        <v>86</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.6511627906976745</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>-0.87</v>
+      </c>
+      <c r="M44" s="10" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="N44" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O44" s="10" t="n">
+        <v>14.34636359571708</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Aggressive 2.43% / 2h</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 comparison</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S44" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
+        </is>
+      </c>
+      <c r="T44" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25T14:58:52+00:00</t>
+        </is>
+      </c>
+      <c r="U44" s="6" t="inlineStr">
+        <is>
+          <t>Public MaxFi config + DexScreener snapshot. Estimate = 24h volume × DEX fee tier ÷ TVL × 85% × 365; not actual MaxFi APR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
         <v>158</v>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>USDG / SGOV</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>0.30%</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr">
         <is>
           <t>0xfAb520051f96F4D2a32c22B6a3dD7fFfdf231bFe</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>stocks</t>
         </is>
       </c>
-      <c r="F44" s="7" t="n">
+      <c r="F45" s="7" t="n">
         <v>2398790.21</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>141343.06</v>
-      </c>
-      <c r="H44" s="8" t="n">
-        <v>0.05892264334362111</v>
-      </c>
-      <c r="I44" s="6" t="n">
+      <c r="G45" s="7" t="n">
+        <v>141339.33</v>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>0.0589210883931363</v>
+      </c>
+      <c r="I45" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J45" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="K44" s="9" t="n">
+      <c r="K45" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="L44" s="10" t="n">
+      <c r="L45" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="M44" s="10" t="n">
+      <c r="M45" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="10" t="n">
+      <c r="N45" s="10" t="n">
         <v>0.01</v>
       </c>
-      <c r="O44" s="10" t="n">
-        <v>5.484225029207535</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
+      <c r="O45" s="10" t="n">
+        <v>5.484080302191161</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
         <is>
           <t>Aggressive 1.2072% / 2h</t>
         </is>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
         <is>
           <t>Tier 1</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S44" s="6" t="inlineStr">
+      <c r="S45" s="6" t="inlineStr">
         <is>
           <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
         </is>
       </c>
-      <c r="T44" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-25T14:58:02+00:00</t>
-        </is>
-      </c>
-      <c r="U44" s="6" t="inlineStr">
+      <c r="T45" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-25T14:58:52+00:00</t>
+        </is>
+      </c>
+      <c r="U45" s="6" t="inlineStr">
         <is>
           <t>Public MaxFi config + DexScreener snapshot. Estimate = 24h volume × DEX fee tier ÷ TVL × 85% × 365; not actual MaxFi APR.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:U44"/>
+  <autoFilter ref="A4:U45"/>
   <mergeCells count="2">
     <mergeCell ref="A1:U1"/>
     <mergeCell ref="A2:U2"/>
   </mergeCells>
-  <conditionalFormatting sqref="O5:O44">
+  <conditionalFormatting sqref="O5:O45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -4530,31 +4615,31 @@
         <v>169584.37</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>485315.01</v>
+        <v>484782.19</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>2.861790918585245</v>
+        <v>2.858649001673916</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J5" s="6" t="n">
         <v>26</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>-0.9</v>
+        <v>-2.17</v>
       </c>
       <c r="M5" s="10" t="n">
         <v>6.64</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>-4.21</v>
+        <v>-3.91</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>887.870632491072</v>
+        <v>886.8958527693325</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -4578,7 +4663,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -4612,34 +4697,34 @@
         </is>
       </c>
       <c r="F6" s="7" t="n">
-        <v>329924.4</v>
+        <v>330071.28</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>925105.77</v>
+        <v>928580.63</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>2.803993187530234</v>
+        <v>2.813273029995218</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>50</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="M6" s="10" t="n">
-        <v>-1.84</v>
+        <v>-1.77</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>-2.31</v>
+        <v>-2.22</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>869.9388864312552</v>
+        <v>872.8179575560164</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
@@ -4663,7 +4748,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -4697,34 +4782,34 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>175882.51</v>
+        <v>176298.97</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>411553.11</v>
+        <v>410613.4</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2.339931980729636</v>
+        <v>2.329074299186206</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>-1.95</v>
+        <v>-1.69</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.06</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>-8.66</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>725.9638970213696</v>
+        <v>722.5953013225204</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -4748,7 +4833,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -4960,34 +5045,34 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>181448.81</v>
+        <v>181121.68</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>740633.3</v>
+        <v>740855.47</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4.081775460527958</v>
+        <v>4.090374327358271</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>15</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>-4.34</v>
+        <v>-4.56</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>-0.63</v>
+        <v>-0.86</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>18.33</v>
+        <v>18.21</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1266.370836628799</v>
+        <v>1269.038635062903</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -5011,7 +5096,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -5054,16 +5139,16 @@
         <v>2.71851644488703</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>-6.08</v>
+        <v>-6.42</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>-3.92</v>
@@ -5096,7 +5181,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -5130,34 +5215,34 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>48200.02</v>
+        <v>48565.22</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>108125.93</v>
+        <v>109697.27</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>2.243275625196836</v>
+        <v>2.258761928804194</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J7" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>2.49</v>
+        <v>3.62</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>-2.28</v>
+        <v>-1.21</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>-4.67</v>
+        <v>-3.28</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>695.9762627173183</v>
+        <v>700.7808884115011</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -5181,7 +5266,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -5196,7 +5281,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>WETH / SCHIFFY</t>
+          <t>WETH / SHROOM</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -5206,7 +5291,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
+          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -5215,38 +5300,38 @@
         </is>
       </c>
       <c r="F8" s="7" t="n">
-        <v>93135.10000000001</v>
+        <v>137831.67</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>207651.04</v>
+        <v>308457.55</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2.229568014636802</v>
+        <v>2.237929425073352</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>-3.72</v>
+        <v>-2.8</v>
       </c>
       <c r="M8" s="10" t="n">
-        <v>-1.73</v>
+        <v>-6.28</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-12.9</v>
+        <v>43.37</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>691.7234765410677</v>
+        <v>694.3176041290075</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 122.55% / 8h</t>
+          <t>Aggressive 231.99% / 8h</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
@@ -5266,7 +5351,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -5281,7 +5366,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>WETH / SHROOM</t>
+          <t>WETH / SCHIFFY</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -5291,7 +5376,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
+          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
@@ -5300,38 +5385,38 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>138129.17</v>
+        <v>93288.14999999999</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>307892.63</v>
+        <v>207701.28</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2.229019619823966</v>
+        <v>2.226448696860212</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>-1.71</v>
+        <v>-3.4</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>-5.55</v>
+        <v>-1.81</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>44.33</v>
+        <v>-12.85</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>691.5533370503854</v>
+        <v>690.7557082008808</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 231.99% / 8h</t>
+          <t>Aggressive 122.55% / 8h</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
@@ -5351,7 +5436,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -5385,34 +5470,34 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>65160.76</v>
+        <v>65178.3</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>129498.07</v>
+        <v>129545.24</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>1.987362793190258</v>
+        <v>1.987551685146744</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>14</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>-5.73</v>
+        <v>-5.36</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>616.5793065872773</v>
+        <v>616.6379103167773</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -5436,7 +5521,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -5451,7 +5536,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>BUN / WETH</t>
+          <t>WETH / HOOKR</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -5461,7 +5546,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
+          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
@@ -5470,38 +5555,38 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>128868.98</v>
+        <v>71219.36</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>222708.94</v>
+        <v>124439.2</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1.72818113404793</v>
+        <v>1.747266473610546</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.3684210526315789</v>
+        <v>0</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>0.79</v>
+        <v>-5.76</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>0.83</v>
+        <v>4.22</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>9.68</v>
+        <v>12.65</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>536.1681968383704</v>
+        <v>542.0894234376721</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 161.16% / 8h</t>
+          <t>Aggressive 49.18% / 8h</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -5521,7 +5606,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -5536,7 +5621,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>WETH / HOOKR</t>
+          <t>BUN / WETH</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -5546,7 +5631,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
+          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -5555,38 +5640,38 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>71546.63</v>
+        <v>129134.65</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>123453.29</v>
+        <v>222772.84</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>1.725494128794046</v>
+        <v>1.725120562141919</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>-4.58</v>
+        <v>1</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>5.53</v>
+        <v>1.04</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>14.73</v>
+        <v>9.92</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>535.3345534583527</v>
+        <v>535.2186544045304</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 49.18% / 8h</t>
+          <t>Aggressive 161.16% / 8h</t>
         </is>
       </c>
       <c r="Q12" s="6" t="inlineStr">
@@ -5606,7 +5691,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -5640,34 +5725,34 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>96148.73</v>
+        <v>96139.41</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>162361.82</v>
+        <v>162384.79</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>1.688652777837003</v>
+        <v>1.689055404022138</v>
       </c>
       <c r="I13" s="6" t="n">
         <v>22</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>8.44</v>
+        <v>8.41</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>20.01</v>
+        <v>19.97</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>-1.47</v>
+        <v>-1.51</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>523.9045243239303</v>
+        <v>524.0294390978685</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -5691,7 +5776,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -5903,34 +5988,34 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>181448.81</v>
+        <v>181121.68</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>740633.3</v>
+        <v>740855.47</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4.081775460527958</v>
+        <v>4.090374327358271</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>15</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>-4.34</v>
+        <v>-4.56</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>-0.63</v>
+        <v>-0.86</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>18.33</v>
+        <v>18.21</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1266.370836628799</v>
+        <v>1269.038635062903</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -5954,7 +6039,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -5991,31 +6076,31 @@
         <v>12993.11</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>50072.79</v>
+        <v>49628.45</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>3.853795588585027</v>
+        <v>3.819597463578773</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>-2.29</v>
+        <v>-2.04</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>-4.9</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>1195.640081358505</v>
+        <v>1185.030113075314</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
@@ -6039,7 +6124,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -6073,34 +6158,34 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>11853.2</v>
+        <v>11868.68</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>40690.36</v>
+        <v>40712.93</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>3.432858637330003</v>
+        <v>3.430282895823293</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>28</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>1</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>6.57</v>
+        <v>7.29</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>16.03</v>
+        <v>16.07</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>1065.044392231634</v>
+        <v>1064.245268429177</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -6124,7 +6209,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -6161,31 +6246,31 @@
         <v>169584.37</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>485315.01</v>
+        <v>484782.19</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2.861790918585245</v>
+        <v>2.858649001673916</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>26</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>-0.9</v>
+        <v>-2.17</v>
       </c>
       <c r="M8" s="10" t="n">
         <v>6.64</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-4.21</v>
+        <v>-3.91</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>887.870632491072</v>
+        <v>886.8958527693325</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -6209,7 +6294,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -6243,34 +6328,34 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>18420.29</v>
+        <v>18441.77</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>50712.07</v>
+        <v>50754.37</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2.753054919330803</v>
+        <v>2.752142012399027</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>53</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>16.41</v>
+        <v>16.75</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>38.87</v>
+        <v>38.8</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>82.81</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>854.1352887223816</v>
+        <v>853.8520593467981</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -6294,7 +6379,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -6337,16 +6422,16 @@
         <v>2.71851644488703</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>11</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>-6.08</v>
+        <v>-6.42</v>
       </c>
       <c r="M10" s="10" t="n">
         <v>-3.92</v>
@@ -6379,7 +6464,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -6413,34 +6498,34 @@
         </is>
       </c>
       <c r="F11" s="7" t="n">
-        <v>175882.51</v>
+        <v>176298.97</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>411553.11</v>
+        <v>410613.4</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>2.339931980729636</v>
+        <v>2.329074299186206</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L11" s="10" t="n">
-        <v>-1.95</v>
+        <v>-1.69</v>
       </c>
       <c r="M11" s="10" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.06</v>
       </c>
       <c r="N11" s="10" t="n">
-        <v>-8.66</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="O11" s="10" t="n">
-        <v>725.9638970213696</v>
+        <v>722.5953013225204</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -6464,7 +6549,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -6498,34 +6583,34 @@
         </is>
       </c>
       <c r="F12" s="7" t="n">
-        <v>48200.02</v>
+        <v>48565.22</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>108125.93</v>
+        <v>109697.27</v>
       </c>
       <c r="H12" s="8" t="n">
-        <v>2.243275625196836</v>
+        <v>2.258761928804194</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>2.49</v>
+        <v>3.62</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>-2.28</v>
+        <v>-1.21</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>-4.67</v>
+        <v>-3.28</v>
       </c>
       <c r="O12" s="10" t="n">
-        <v>695.9762627173183</v>
+        <v>700.7808884115011</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -6549,7 +6634,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -6564,7 +6649,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>WETH / SCHIFFY</t>
+          <t>WETH / SHROOM</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -6574,7 +6659,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
+          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -6583,38 +6668,38 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>93135.10000000001</v>
+        <v>137831.67</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>207651.04</v>
+        <v>308457.55</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>2.229568014636802</v>
+        <v>2.237929425073352</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-3.72</v>
+        <v>-2.8</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-1.73</v>
+        <v>-6.28</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>-12.9</v>
+        <v>43.37</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>691.7234765410677</v>
+        <v>694.3176041290075</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 122.55% / 8h</t>
+          <t>Aggressive 231.99% / 8h</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
@@ -6634,7 +6719,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -6649,7 +6734,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>WETH / SHROOM</t>
+          <t>WETH / SCHIFFY</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -6659,7 +6744,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
+          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -6668,38 +6753,38 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>138129.17</v>
+        <v>93288.14999999999</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>307892.63</v>
+        <v>207701.28</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>2.229019619823966</v>
+        <v>2.226448696860212</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>-1.71</v>
+        <v>-3.4</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>-5.55</v>
+        <v>-1.81</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>44.33</v>
+        <v>-12.85</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>691.5533370503854</v>
+        <v>690.7557082008808</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 231.99% / 8h</t>
+          <t>Aggressive 122.55% / 8h</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
@@ -6719,7 +6804,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -6804,7 +6889,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -6838,34 +6923,34 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>65160.76</v>
+        <v>65178.3</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>129498.07</v>
+        <v>129545.24</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>1.987362793190258</v>
+        <v>1.987551685146744</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>14</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>-5.73</v>
+        <v>-5.36</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>616.5793065872773</v>
+        <v>616.6379103167773</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -6889,7 +6974,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -6974,7 +7059,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -7059,7 +7144,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -7144,7 +7229,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -7159,7 +7244,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BUN / WETH</t>
+          <t>WETH / HOOKR</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -7169,7 +7254,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
+          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -7178,38 +7263,38 @@
         </is>
       </c>
       <c r="F20" s="7" t="n">
-        <v>128868.98</v>
+        <v>71219.36</v>
       </c>
       <c r="G20" s="7" t="n">
-        <v>222708.94</v>
+        <v>124439.2</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>1.72818113404793</v>
+        <v>1.747266473610546</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.3684210526315789</v>
+        <v>0</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>0.79</v>
+        <v>-5.76</v>
       </c>
       <c r="M20" s="10" t="n">
-        <v>0.83</v>
+        <v>4.22</v>
       </c>
       <c r="N20" s="10" t="n">
-        <v>9.68</v>
+        <v>12.65</v>
       </c>
       <c r="O20" s="10" t="n">
-        <v>536.1681968383704</v>
+        <v>542.0894234376721</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 161.16% / 8h</t>
+          <t>Aggressive 49.18% / 8h</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
@@ -7229,7 +7314,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -7244,7 +7329,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>WETH / HOOKR</t>
+          <t>BUN / WETH</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -7254,7 +7339,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
+          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -7263,38 +7348,38 @@
         </is>
       </c>
       <c r="F21" s="7" t="n">
-        <v>71546.63</v>
+        <v>129134.65</v>
       </c>
       <c r="G21" s="7" t="n">
-        <v>123453.29</v>
+        <v>222772.84</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>1.725494128794046</v>
+        <v>1.725120562141919</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L21" s="10" t="n">
-        <v>-4.58</v>
+        <v>1</v>
       </c>
       <c r="M21" s="10" t="n">
-        <v>5.53</v>
+        <v>1.04</v>
       </c>
       <c r="N21" s="10" t="n">
-        <v>14.73</v>
+        <v>9.92</v>
       </c>
       <c r="O21" s="10" t="n">
-        <v>535.3345534583527</v>
+        <v>535.2186544045304</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 49.18% / 8h</t>
+          <t>Aggressive 161.16% / 8h</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
@@ -7314,7 +7399,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -7526,34 +7611,34 @@
         </is>
       </c>
       <c r="F5" s="7" t="n">
-        <v>181448.81</v>
+        <v>181121.68</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>740633.3</v>
+        <v>740855.47</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>4.081775460527958</v>
+        <v>4.090374327358271</v>
       </c>
       <c r="I5" s="6" t="n">
         <v>15</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.3409090909090909</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>-4.34</v>
+        <v>-4.56</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>-0.63</v>
+        <v>-0.86</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>18.33</v>
+        <v>18.21</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>1266.370836628799</v>
+        <v>1269.038635062903</v>
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
@@ -7577,7 +7662,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -7614,31 +7699,31 @@
         <v>12993.11</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>50072.79</v>
+        <v>49628.45</v>
       </c>
       <c r="H6" s="8" t="n">
-        <v>3.853795588585027</v>
+        <v>3.819597463578773</v>
       </c>
       <c r="I6" s="6" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>-2.29</v>
+        <v>-2.04</v>
       </c>
       <c r="M6" s="10" t="n">
         <v>1.02</v>
       </c>
       <c r="N6" s="10" t="n">
-        <v>-4.9</v>
+        <v>-9.9</v>
       </c>
       <c r="O6" s="10" t="n">
-        <v>1195.640081358505</v>
+        <v>1185.030113075314</v>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
@@ -7662,7 +7747,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -7696,34 +7781,34 @@
         </is>
       </c>
       <c r="F7" s="7" t="n">
-        <v>11853.2</v>
+        <v>11868.68</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>40690.36</v>
+        <v>40712.93</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>3.432858637330003</v>
+        <v>3.430282895823293</v>
       </c>
       <c r="I7" s="6" t="n">
         <v>28</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>1</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>6.57</v>
+        <v>7.29</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>16.03</v>
+        <v>16.07</v>
       </c>
       <c r="O7" s="10" t="n">
-        <v>1065.044392231634</v>
+        <v>1064.245268429177</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -7747,7 +7832,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -7784,31 +7869,31 @@
         <v>169584.37</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>485315.01</v>
+        <v>484782.19</v>
       </c>
       <c r="H8" s="8" t="n">
-        <v>2.861790918585245</v>
+        <v>2.858649001673916</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>26</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.7307692307692307</v>
+        <v>0.6923076923076923</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>-0.9</v>
+        <v>-2.17</v>
       </c>
       <c r="M8" s="10" t="n">
         <v>6.64</v>
       </c>
       <c r="N8" s="10" t="n">
-        <v>-4.21</v>
+        <v>-3.91</v>
       </c>
       <c r="O8" s="10" t="n">
-        <v>887.870632491072</v>
+        <v>886.8958527693325</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -7832,7 +7917,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -7866,34 +7951,34 @@
         </is>
       </c>
       <c r="F9" s="7" t="n">
-        <v>329924.4</v>
+        <v>330071.28</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>925105.77</v>
+        <v>928580.63</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>2.803993187530234</v>
+        <v>2.813273029995218</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>50</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="L9" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="M9" s="10" t="n">
-        <v>-1.84</v>
+        <v>-1.77</v>
       </c>
       <c r="N9" s="10" t="n">
-        <v>-2.31</v>
+        <v>-2.22</v>
       </c>
       <c r="O9" s="10" t="n">
-        <v>869.9388864312552</v>
+        <v>872.8179575560164</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -7917,7 +8002,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -7951,34 +8036,34 @@
         </is>
       </c>
       <c r="F10" s="7" t="n">
-        <v>18420.29</v>
+        <v>18441.77</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>50712.07</v>
+        <v>50754.37</v>
       </c>
       <c r="H10" s="8" t="n">
-        <v>2.753054919330803</v>
+        <v>2.752142012399027</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J10" s="6" t="n">
         <v>53</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.9056603773584906</v>
+        <v>0.9245283018867925</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>16.41</v>
+        <v>16.75</v>
       </c>
       <c r="M10" s="10" t="n">
-        <v>38.87</v>
+        <v>38.8</v>
       </c>
       <c r="N10" s="10" t="n">
-        <v>82.81</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>854.1352887223816</v>
+        <v>853.8520593467981</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -8002,7 +8087,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -8087,7 +8172,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -8130,16 +8215,16 @@
         <v>2.71851644488703</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>11</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>-6.08</v>
+        <v>-6.42</v>
       </c>
       <c r="M12" s="10" t="n">
         <v>-3.92</v>
@@ -8172,7 +8257,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -8206,34 +8291,34 @@
         </is>
       </c>
       <c r="F13" s="7" t="n">
-        <v>175882.51</v>
+        <v>176298.97</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>411553.11</v>
+        <v>410613.4</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>2.339931980729636</v>
+        <v>2.329074299186206</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>21</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-1.95</v>
+        <v>-1.69</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-9.300000000000001</v>
+        <v>-9.06</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>-8.66</v>
+        <v>-8.390000000000001</v>
       </c>
       <c r="O13" s="10" t="n">
-        <v>725.9638970213696</v>
+        <v>722.5953013225204</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -8257,7 +8342,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -8291,34 +8376,34 @@
         </is>
       </c>
       <c r="F14" s="7" t="n">
-        <v>48200.02</v>
+        <v>48565.22</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>108125.93</v>
+        <v>109697.27</v>
       </c>
       <c r="H14" s="8" t="n">
-        <v>2.243275625196836</v>
+        <v>2.258761928804194</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>15</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>2.49</v>
+        <v>3.62</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>-2.28</v>
+        <v>-1.21</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>-4.67</v>
+        <v>-3.28</v>
       </c>
       <c r="O14" s="10" t="n">
-        <v>695.9762627173183</v>
+        <v>700.7808884115011</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -8342,7 +8427,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -8357,7 +8442,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>WETH / SCHIFFY</t>
+          <t>WETH / SHROOM</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -8367,7 +8452,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
+          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -8376,38 +8461,38 @@
         </is>
       </c>
       <c r="F15" s="7" t="n">
-        <v>93135.10000000001</v>
+        <v>137831.67</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>207651.04</v>
+        <v>308457.55</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>2.229568014636802</v>
+        <v>2.237929425073352</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.8095238095238095</v>
       </c>
       <c r="L15" s="10" t="n">
-        <v>-3.72</v>
+        <v>-2.8</v>
       </c>
       <c r="M15" s="10" t="n">
-        <v>-1.73</v>
+        <v>-6.28</v>
       </c>
       <c r="N15" s="10" t="n">
-        <v>-12.9</v>
+        <v>43.37</v>
       </c>
       <c r="O15" s="10" t="n">
-        <v>691.7234765410677</v>
+        <v>694.3176041290075</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 122.55% / 8h</t>
+          <t>Aggressive 231.99% / 8h</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
@@ -8427,7 +8512,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -8442,7 +8527,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>WETH / SHROOM</t>
+          <t>WETH / SCHIFFY</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -8452,7 +8537,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>0xC641a0DC848E7aadd7c69d800BAE2FEA9b258610</t>
+          <t>0x417e0A3A9d03ddEe6749f21Aa02498338A652786</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -8461,38 +8546,38 @@
         </is>
       </c>
       <c r="F16" s="7" t="n">
-        <v>138129.17</v>
+        <v>93288.14999999999</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>307892.63</v>
+        <v>207701.28</v>
       </c>
       <c r="H16" s="8" t="n">
-        <v>2.229019619823966</v>
+        <v>2.226448696860212</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.7307692307692307</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-1.71</v>
+        <v>-3.4</v>
       </c>
       <c r="M16" s="10" t="n">
-        <v>-5.55</v>
+        <v>-1.81</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>44.33</v>
+        <v>-12.85</v>
       </c>
       <c r="O16" s="10" t="n">
-        <v>691.5533370503854</v>
+        <v>690.7557082008808</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 231.99% / 8h</t>
+          <t>Aggressive 122.55% / 8h</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
@@ -8512,7 +8597,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -8597,7 +8682,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -8631,34 +8716,34 @@
         </is>
       </c>
       <c r="F18" s="7" t="n">
-        <v>65160.76</v>
+        <v>65178.3</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>129498.07</v>
+        <v>129545.24</v>
       </c>
       <c r="H18" s="8" t="n">
-        <v>1.987362793190258</v>
+        <v>1.987551685146744</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="6" t="n">
         <v>14</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="M18" s="10" t="n">
-        <v>-5.73</v>
+        <v>-5.36</v>
       </c>
       <c r="N18" s="10" t="n">
-        <v>-9.119999999999999</v>
+        <v>-9.07</v>
       </c>
       <c r="O18" s="10" t="n">
-        <v>616.5793065872773</v>
+        <v>616.6379103167773</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -8682,7 +8767,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -8767,7 +8852,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -8852,7 +8937,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -8937,7 +9022,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -8952,7 +9037,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>BUN / WETH</t>
+          <t>WETH / HOOKR</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -8962,7 +9047,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
+          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -8971,38 +9056,38 @@
         </is>
       </c>
       <c r="F22" s="7" t="n">
-        <v>128868.98</v>
+        <v>71219.36</v>
       </c>
       <c r="G22" s="7" t="n">
-        <v>222708.94</v>
+        <v>124439.2</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>1.72818113404793</v>
+        <v>1.747266473610546</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.3684210526315789</v>
+        <v>0</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>0.79</v>
+        <v>-5.76</v>
       </c>
       <c r="M22" s="10" t="n">
-        <v>0.83</v>
+        <v>4.22</v>
       </c>
       <c r="N22" s="10" t="n">
-        <v>9.68</v>
+        <v>12.65</v>
       </c>
       <c r="O22" s="10" t="n">
-        <v>536.1681968383704</v>
+        <v>542.0894234376721</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 161.16% / 8h</t>
+          <t>Aggressive 49.18% / 8h</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
@@ -9022,7 +9107,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -9037,7 +9122,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>WETH / HOOKR</t>
+          <t>BUN / WETH</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -9047,7 +9132,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>0x42b19e5e3F28C4148C518444546f102F6ba87aB1</t>
+          <t>0x4F22b1A543711903604d5E84333A9FdD4A63166d</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
@@ -9056,38 +9141,38 @@
         </is>
       </c>
       <c r="F23" s="7" t="n">
-        <v>71546.63</v>
+        <v>129134.65</v>
       </c>
       <c r="G23" s="7" t="n">
-        <v>123453.29</v>
+        <v>222772.84</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>1.725494128794046</v>
+        <v>1.725120562141919</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0</v>
+        <v>0.3684210526315789</v>
       </c>
       <c r="L23" s="10" t="n">
-        <v>-4.58</v>
+        <v>1</v>
       </c>
       <c r="M23" s="10" t="n">
-        <v>5.53</v>
+        <v>1.04</v>
       </c>
       <c r="N23" s="10" t="n">
-        <v>14.73</v>
+        <v>9.92</v>
       </c>
       <c r="O23" s="10" t="n">
-        <v>535.3345534583527</v>
+        <v>535.2186544045304</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 49.18% / 8h</t>
+          <t>Aggressive 161.16% / 8h</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
@@ -9107,7 +9192,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -9141,34 +9226,34 @@
         </is>
       </c>
       <c r="F24" s="7" t="n">
-        <v>96148.73</v>
+        <v>96139.41</v>
       </c>
       <c r="G24" s="7" t="n">
-        <v>162361.82</v>
+        <v>162384.79</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>1.688652777837003</v>
+        <v>1.689055404022138</v>
       </c>
       <c r="I24" s="6" t="n">
         <v>22</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>8.44</v>
+        <v>8.41</v>
       </c>
       <c r="M24" s="10" t="n">
-        <v>20.01</v>
+        <v>19.97</v>
       </c>
       <c r="N24" s="10" t="n">
-        <v>-1.47</v>
+        <v>-1.51</v>
       </c>
       <c r="O24" s="10" t="n">
-        <v>523.9045243239303</v>
+        <v>524.0294390978685</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -9192,7 +9277,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -9229,31 +9314,31 @@
         <v>444029.22</v>
       </c>
       <c r="G25" s="7" t="n">
-        <v>646286.55</v>
+        <v>645888.45</v>
       </c>
       <c r="H25" s="8" t="n">
-        <v>1.45550454990327</v>
+        <v>1.454607987285161</v>
       </c>
       <c r="I25" s="6" t="n">
         <v>18</v>
       </c>
       <c r="J25" s="6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.9</v>
       </c>
       <c r="L25" s="10" t="n">
-        <v>1.96</v>
+        <v>1.66</v>
       </c>
       <c r="M25" s="10" t="n">
         <v>6.53</v>
       </c>
       <c r="N25" s="10" t="n">
-        <v>5.24</v>
+        <v>5.33</v>
       </c>
       <c r="O25" s="10" t="n">
-        <v>451.5702866074895</v>
+        <v>451.2921280552213</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -9277,7 +9362,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -9362,7 +9447,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -9447,7 +9532,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -9532,7 +9617,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -9569,10 +9654,10 @@
         <v>6764.11</v>
       </c>
       <c r="G29" s="7" t="n">
-        <v>6950.29</v>
+        <v>6911.08</v>
       </c>
       <c r="H29" s="8" t="n">
-        <v>1.027524685435334</v>
+        <v>1.021727913945811</v>
       </c>
       <c r="I29" s="6" t="n">
         <v>5</v>
@@ -9590,10 +9675,10 @@
         <v>1.72</v>
       </c>
       <c r="N29" s="10" t="n">
-        <v>-17.57</v>
+        <v>-17.25</v>
       </c>
       <c r="O29" s="10" t="n">
-        <v>318.7895336563125</v>
+        <v>316.9910853016879</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -9617,7 +9702,7 @@
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -9654,31 +9739,31 @@
         <v>77099.08</v>
       </c>
       <c r="G30" s="7" t="n">
-        <v>74768.08</v>
+        <v>74758.16</v>
       </c>
       <c r="H30" s="8" t="n">
-        <v>0.9697661761982115</v>
+        <v>0.969637510590269</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J30" s="6" t="n">
         <v>29</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>1</v>
+        <v>0.9655172413793104</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>4.7</v>
+        <v>4.69</v>
       </c>
       <c r="M30" s="10" t="n">
-        <v>-6.29</v>
+        <v>-6.31</v>
       </c>
       <c r="N30" s="10" t="n">
         <v>-18.8</v>
       </c>
       <c r="O30" s="10" t="n">
-        <v>300.8699561654951</v>
+        <v>300.830037660631</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -9702,7 +9787,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -9739,10 +9824,10 @@
         <v>26256.32</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>80998.16</v>
+        <v>80930.46000000001</v>
       </c>
       <c r="H31" s="8" t="n">
-        <v>3.084901463723782</v>
+        <v>3.082323036891689</v>
       </c>
       <c r="I31" s="6" t="n">
         <v>24</v>
@@ -9757,13 +9842,13 @@
         <v>-1.95</v>
       </c>
       <c r="M31" s="10" t="n">
-        <v>-4.93</v>
+        <v>-5.06</v>
       </c>
       <c r="N31" s="10" t="n">
-        <v>-13.21</v>
+        <v>-13.23</v>
       </c>
       <c r="O31" s="10" t="n">
-        <v>287.1272037360909</v>
+        <v>286.8872166586941</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -9787,7 +9872,7 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -9872,7 +9957,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -9957,7 +10042,7 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -9991,34 +10076,34 @@
         </is>
       </c>
       <c r="F34" s="7" t="n">
-        <v>464541.32</v>
+        <v>464540.71</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>1393323.29</v>
+        <v>1388167.72</v>
       </c>
       <c r="H34" s="8" t="n">
-        <v>2.999352759405773</v>
+        <v>2.988258488690905</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="J34" s="6" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.9583333333333334</v>
+        <v>0.9759036144578314</v>
       </c>
       <c r="L34" s="10" t="n">
         <v>-0.96</v>
       </c>
       <c r="M34" s="10" t="n">
-        <v>-3.24</v>
+        <v>-3.23</v>
       </c>
       <c r="N34" s="10" t="n">
-        <v>-2.28</v>
+        <v>-2.54</v>
       </c>
       <c r="O34" s="10" t="n">
-        <v>279.1647580816922</v>
+        <v>278.132158834906</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -10042,7 +10127,7 @@
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -10076,13 +10161,13 @@
         </is>
       </c>
       <c r="F35" s="7" t="n">
-        <v>30526.6</v>
+        <v>30649.06</v>
       </c>
       <c r="G35" s="7" t="n">
-        <v>25568.78</v>
+        <v>25611.96</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.83759016726396</v>
+        <v>0.8356523821611495</v>
       </c>
       <c r="I35" s="6" t="n">
         <v>20</v>
@@ -10094,16 +10179,16 @@
         <v>0.8</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>5.55</v>
+        <v>5.61</v>
       </c>
       <c r="M35" s="10" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="N35" s="10" t="n">
-        <v>-7.25</v>
+        <v>-6.63</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>259.8623493936436</v>
+        <v>259.2611515654966</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -10127,7 +10212,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -10212,7 +10297,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -10297,7 +10382,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -10331,34 +10416,34 @@
         </is>
       </c>
       <c r="F38" s="7" t="n">
-        <v>112644.61</v>
+        <v>112786.68</v>
       </c>
       <c r="G38" s="7" t="n">
-        <v>86308.06</v>
+        <v>86113.78</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.7661978677896794</v>
+        <v>0.763510194643552</v>
       </c>
       <c r="I38" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J38" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.625</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>-2.99</v>
+        <v>-2.92</v>
       </c>
       <c r="M38" s="10" t="n">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="N38" s="10" t="n">
-        <v>-17.93</v>
+        <v>-17.64</v>
       </c>
       <c r="O38" s="10" t="n">
-        <v>237.7128884817481</v>
+        <v>236.879037888162</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -10382,7 +10467,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -10416,34 +10501,34 @@
         </is>
       </c>
       <c r="F39" s="7" t="n">
-        <v>4654.52</v>
+        <v>4651.08</v>
       </c>
       <c r="G39" s="7" t="n">
-        <v>3452.32</v>
+        <v>3464.48</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.7417134312453271</v>
+        <v>0.7448764588009666</v>
       </c>
       <c r="I39" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J39" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="L39" s="10" t="n">
-        <v>-1.73</v>
+        <v>-1.85</v>
       </c>
       <c r="M39" s="10" t="n">
-        <v>0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N39" s="10" t="n">
-        <v>3.77</v>
+        <v>3.64</v>
       </c>
       <c r="O39" s="10" t="n">
-        <v>230.1165920438627</v>
+        <v>231.0979213429999</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -10467,7 +10552,7 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -10522,7 +10607,7 @@
         <v>2.86</v>
       </c>
       <c r="M40" s="10" t="n">
-        <v>-0.48</v>
+        <v>-1.99</v>
       </c>
       <c r="N40" s="10" t="n">
         <v>5.17</v>
@@ -10552,7 +10637,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -10589,19 +10674,19 @@
         <v>201422.74</v>
       </c>
       <c r="G41" s="7" t="n">
-        <v>485795.18</v>
+        <v>485324.21</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>2.411818943581048</v>
+        <v>2.409480726952677</v>
       </c>
       <c r="I41" s="6" t="n">
         <v>29</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.7931034482758621</v>
       </c>
       <c r="L41" s="10" t="n">
         <v>-0.18</v>
@@ -10610,10 +10695,10 @@
         <v>0.01</v>
       </c>
       <c r="N41" s="10" t="n">
-        <v>-1.68</v>
+        <v>-1.81</v>
       </c>
       <c r="O41" s="10" t="n">
-        <v>224.480048173806</v>
+        <v>224.2624186611204</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -10637,7 +10722,7 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -10680,16 +10765,16 @@
         <v>2.256887870684372</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="J42" s="6" t="n">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.9562043795620438</v>
+        <v>0.9774436090225563</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="M42" s="10" t="n">
         <v>3.87</v>
@@ -10722,7 +10807,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -10807,7 +10892,7 @@
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -10841,13 +10926,13 @@
         </is>
       </c>
       <c r="F44" s="7" t="n">
-        <v>540221.3</v>
+        <v>540093.92</v>
       </c>
       <c r="G44" s="7" t="n">
-        <v>357253.56</v>
+        <v>357384.68</v>
       </c>
       <c r="H44" s="8" t="n">
-        <v>0.6613096521740257</v>
+        <v>0.6617083932364948</v>
       </c>
       <c r="I44" s="6" t="n">
         <v>26</v>
@@ -10859,16 +10944,16 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="M44" s="10" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N44" s="10" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="O44" s="10" t="n">
-        <v>205.1713195869914</v>
+        <v>205.2950290016225</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -10892,7 +10977,7 @@
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -10977,7 +11062,7 @@
       </c>
       <c r="T45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U45" s="6" t="inlineStr">
@@ -11011,34 +11096,34 @@
         </is>
       </c>
       <c r="F46" s="7" t="n">
-        <v>276548</v>
+        <v>277089.22</v>
       </c>
       <c r="G46" s="7" t="n">
-        <v>176664.49</v>
+        <v>176665.09</v>
       </c>
       <c r="H46" s="8" t="n">
-        <v>0.6388203494510898</v>
+        <v>0.6375747493893844</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J46" s="6" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>-0.02</v>
+        <v>0.18</v>
       </c>
       <c r="M46" s="10" t="n">
-        <v>2.58</v>
+        <v>2.78</v>
       </c>
       <c r="N46" s="10" t="n">
-        <v>-3.32</v>
+        <v>-3.13</v>
       </c>
       <c r="O46" s="10" t="n">
-        <v>198.1940134172006</v>
+        <v>197.8075659980566</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -11062,7 +11147,7 @@
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
@@ -11096,34 +11181,34 @@
         </is>
       </c>
       <c r="F47" s="7" t="n">
-        <v>156558.25</v>
+        <v>158680.03</v>
       </c>
       <c r="G47" s="7" t="n">
-        <v>1992933.11</v>
+        <v>1993233.02</v>
       </c>
       <c r="H47" s="8" t="n">
-        <v>12.72965883305415</v>
+        <v>12.56133503377835</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J47" s="6" t="n">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.9195402298850575</v>
+        <v>0.9192307692307692</v>
       </c>
       <c r="L47" s="10" t="n">
-        <v>-2.68</v>
+        <v>-2.71</v>
       </c>
       <c r="M47" s="10" t="n">
-        <v>-6.72</v>
+        <v>-6.85</v>
       </c>
       <c r="N47" s="10" t="n">
-        <v>-3.62</v>
+        <v>-3.66</v>
       </c>
       <c r="O47" s="10" t="n">
-        <v>197.4688326477525</v>
+        <v>194.8577097114867</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -11147,7 +11232,7 @@
       </c>
       <c r="T47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U47" s="6" t="inlineStr">
@@ -11232,7 +11317,7 @@
       </c>
       <c r="T48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U48" s="6" t="inlineStr">
@@ -11269,10 +11354,10 @@
         <v>681068.66</v>
       </c>
       <c r="G49" s="7" t="n">
-        <v>412199.7</v>
+        <v>411902.22</v>
       </c>
       <c r="H49" s="8" t="n">
-        <v>0.605224882906813</v>
+        <v>0.6047880987505723</v>
       </c>
       <c r="I49" s="6" t="n">
         <v>11</v>
@@ -11287,13 +11372,13 @@
         <v>1.25</v>
       </c>
       <c r="M49" s="10" t="n">
-        <v>6.59</v>
+        <v>6.24</v>
       </c>
       <c r="N49" s="10" t="n">
-        <v>3.27</v>
+        <v>3.42</v>
       </c>
       <c r="O49" s="10" t="n">
-        <v>187.7710199218387</v>
+        <v>187.635507637365</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -11317,7 +11402,7 @@
       </c>
       <c r="T49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U49" s="6" t="inlineStr">
@@ -11332,17 +11417,17 @@
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>USDG / RBLX</t>
+          <t>WETH / GME</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>0x2ef5945cd5664876b6481FdacFaA2942995a4DA8</t>
+          <t>0xc6BCC95043DC48C204bB2D57fb264a10Efe0a607</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -11351,38 +11436,38 @@
         </is>
       </c>
       <c r="F50" s="7" t="n">
-        <v>214102.43</v>
+        <v>62526.42</v>
       </c>
       <c r="G50" s="7" t="n">
-        <v>127022.16</v>
+        <v>741610.85</v>
       </c>
       <c r="H50" s="8" t="n">
-        <v>0.5932775260887978</v>
+        <v>11.86075981960905</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>5</v>
+        <v>230</v>
       </c>
       <c r="J50" s="6" t="n">
-        <v>15</v>
+        <v>214</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.9304347826086956</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>-1.55</v>
+        <v>-2.94</v>
       </c>
       <c r="M50" s="10" t="n">
-        <v>-2.34</v>
+        <v>-6.83</v>
       </c>
       <c r="N50" s="10" t="n">
-        <v>-3.95</v>
+        <v>-3.92</v>
       </c>
       <c r="O50" s="10" t="n">
-        <v>184.0643524690495</v>
+        <v>183.9900367016855</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 12.75% / 2h</t>
+          <t>Aggressive 7.5% / 2h</t>
         </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
@@ -11402,7 +11487,7 @@
       </c>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U50" s="6" t="inlineStr">
@@ -11417,17 +11502,17 @@
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>WETH / GME</t>
+          <t>USDG / RBLX</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>0xc6BCC95043DC48C204bB2D57fb264a10Efe0a607</t>
+          <t>0x2ef5945cd5664876b6481FdacFaA2942995a4DA8</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
@@ -11436,38 +11521,38 @@
         </is>
       </c>
       <c r="F51" s="7" t="n">
-        <v>62596.01</v>
+        <v>214102.43</v>
       </c>
       <c r="G51" s="7" t="n">
-        <v>740759.34</v>
+        <v>126880.75</v>
       </c>
       <c r="H51" s="8" t="n">
-        <v>11.83397056777261</v>
+        <v>0.5926170478307976</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>228</v>
+        <v>5</v>
       </c>
       <c r="J51" s="6" t="n">
-        <v>215</v>
+        <v>15</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.9429824561403509</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L51" s="10" t="n">
-        <v>-2.99</v>
+        <v>-1.55</v>
       </c>
       <c r="M51" s="10" t="n">
-        <v>-6.68</v>
+        <v>-2.34</v>
       </c>
       <c r="N51" s="10" t="n">
-        <v>-3.8</v>
+        <v>-3.93</v>
       </c>
       <c r="O51" s="10" t="n">
-        <v>183.5744684325726</v>
+        <v>183.859439089505</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 7.5% / 2h</t>
+          <t>Aggressive 12.75% / 2h</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
@@ -11487,7 +11572,7 @@
       </c>
       <c r="T51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U51" s="6" t="inlineStr">
@@ -11521,34 +11606,34 @@
         </is>
       </c>
       <c r="F52" s="7" t="n">
-        <v>250818.54</v>
+        <v>250811.61</v>
       </c>
       <c r="G52" s="7" t="n">
-        <v>493179.62</v>
+        <v>493112.79</v>
       </c>
       <c r="H52" s="8" t="n">
-        <v>1.966280562832396</v>
+        <v>1.966068436784087</v>
       </c>
       <c r="I52" s="6" t="n">
         <v>39</v>
       </c>
       <c r="J52" s="6" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.3277310924369748</v>
+        <v>0.3223140495867768</v>
       </c>
       <c r="L52" s="10" t="n">
         <v>-1</v>
       </c>
       <c r="M52" s="10" t="n">
-        <v>-3.36</v>
+        <v>-3.37</v>
       </c>
       <c r="N52" s="10" t="n">
         <v>-2.49</v>
       </c>
       <c r="O52" s="10" t="n">
-        <v>183.0115633856253</v>
+        <v>182.9918197536789</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -11572,7 +11657,7 @@
       </c>
       <c r="T52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U52" s="6" t="inlineStr">
@@ -11657,7 +11742,7 @@
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U53" s="6" t="inlineStr">
@@ -11712,7 +11797,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M54" s="10" t="n">
-        <v>5.75</v>
+        <v>5.56</v>
       </c>
       <c r="N54" s="10" t="n">
         <v>2.35</v>
@@ -11742,7 +11827,7 @@
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U54" s="6" t="inlineStr">
@@ -11827,7 +11912,7 @@
       </c>
       <c r="T55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U55" s="6" t="inlineStr">
@@ -11864,10 +11949,10 @@
         <v>3295091.66</v>
       </c>
       <c r="G56" s="7" t="n">
-        <v>1709069.37</v>
+        <v>1708860.65</v>
       </c>
       <c r="H56" s="8" t="n">
-        <v>0.5186712681613234</v>
+        <v>0.5186079254620795</v>
       </c>
       <c r="I56" s="6" t="n">
         <v>3</v>
@@ -11882,13 +11967,13 @@
         <v>-1.32</v>
       </c>
       <c r="M56" s="10" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="N56" s="10" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="O56" s="10" t="n">
-        <v>160.9177609470505</v>
+        <v>160.8981088746102</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -11912,7 +11997,7 @@
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
@@ -11927,77 +12012,77 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>MRNA / USDG</t>
+          <t>WETH / VIRTUAL</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.30%</t>
         </is>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>0xA34d0667334074DF2d5BfD259e79E6B9cf1fA8Bf</t>
+          <t>0x7a11bC7f32AEA2f81E83DA399C70315d9662869C</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>altcoin</t>
         </is>
       </c>
       <c r="F57" s="7" t="n">
-        <v>100769.56</v>
+        <v>466196.16</v>
       </c>
       <c r="G57" s="7" t="n">
-        <v>52098.51</v>
+        <v>803978.08</v>
       </c>
       <c r="H57" s="8" t="n">
-        <v>0.5170064253530531</v>
+        <v>1.72454891091338</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="L57" s="10" t="n">
-        <v>-0.2</v>
+        <v>-0.25</v>
       </c>
       <c r="M57" s="10" t="n">
-        <v>-1.57</v>
+        <v>0.39</v>
       </c>
       <c r="N57" s="10" t="n">
-        <v>4.01</v>
+        <v>7.32</v>
       </c>
       <c r="O57" s="10" t="n">
-        <v>160.4012434657847</v>
+        <v>160.5123898832629</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 27.12% / 2h</t>
+          <t>Aggressive 10% / 1h</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>Watch — thin / low activity</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S57" s="6" t="inlineStr">
         <is>
-          <t>below 500% growth screen</t>
+          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
         </is>
       </c>
       <c r="T57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U57" s="6" t="inlineStr">
@@ -12012,77 +12097,77 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>WETH / VIRTUAL</t>
+          <t>MRNA / USDG</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>0x7a11bC7f32AEA2f81E83DA399C70315d9662869C</t>
+          <t>0xA34d0667334074DF2d5BfD259e79E6B9cf1fA8Bf</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>altcoin</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F58" s="7" t="n">
-        <v>466053.49</v>
+        <v>100769.56</v>
       </c>
       <c r="G58" s="7" t="n">
-        <v>802430.85</v>
+        <v>52098.51</v>
       </c>
       <c r="H58" s="8" t="n">
-        <v>1.72175698115682</v>
+        <v>0.5170064253530531</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J58" s="6" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="M58" s="10" t="n">
-        <v>0.3</v>
+        <v>-1.57</v>
       </c>
       <c r="N58" s="10" t="n">
-        <v>7.22</v>
+        <v>4.01</v>
       </c>
       <c r="O58" s="10" t="n">
-        <v>160.252531021171</v>
+        <v>160.4012434657847</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 10% / 1h</t>
+          <t>Aggressive 27.12% / 2h</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Watch — thin / low activity</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S58" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
+          <t>below 500% growth screen</t>
         </is>
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
@@ -12137,7 +12222,7 @@
         <v>0.04</v>
       </c>
       <c r="M59" s="10" t="n">
-        <v>-5.47</v>
+        <v>-5.71</v>
       </c>
       <c r="N59" s="10" t="n">
         <v>17.52</v>
@@ -12167,7 +12252,7 @@
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U59" s="6" t="inlineStr">
@@ -12210,19 +12295,19 @@
         <v>0.4891069649569629</v>
       </c>
       <c r="I60" s="6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J60" s="6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7241379310344828</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>31.15</v>
+        <v>30.29</v>
       </c>
       <c r="M60" s="10" t="n">
-        <v>35.45</v>
+        <v>35.5</v>
       </c>
       <c r="N60" s="10" t="n">
         <v>60.5</v>
@@ -12252,7 +12337,7 @@
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U60" s="6" t="inlineStr">
@@ -12337,7 +12422,7 @@
       </c>
       <c r="T61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U61" s="6" t="inlineStr">
@@ -12374,10 +12459,10 @@
         <v>253995.65</v>
       </c>
       <c r="G62" s="7" t="n">
-        <v>112633.1</v>
+        <v>112261.51</v>
       </c>
       <c r="H62" s="8" t="n">
-        <v>0.4434449960068214</v>
+        <v>0.4419820181959809</v>
       </c>
       <c r="I62" s="6" t="n">
         <v>21</v>
@@ -12395,10 +12480,10 @@
         <v>2.44</v>
       </c>
       <c r="N62" s="10" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="O62" s="10" t="n">
-        <v>137.5788100111163</v>
+        <v>137.1249211453031</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -12422,7 +12507,7 @@
       </c>
       <c r="T62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U62" s="6" t="inlineStr">
@@ -12507,7 +12592,7 @@
       </c>
       <c r="T63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U63" s="6" t="inlineStr">
@@ -12553,16 +12638,16 @@
         <v>55</v>
       </c>
       <c r="J64" s="6" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.8208955223880597</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="M64" s="10" t="n">
-        <v>-2.08</v>
+        <v>-2.17</v>
       </c>
       <c r="N64" s="10" t="n">
         <v>2.16</v>
@@ -12592,7 +12677,7 @@
       </c>
       <c r="T64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U64" s="6" t="inlineStr">
@@ -12677,7 +12762,7 @@
       </c>
       <c r="T65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr">
@@ -12723,16 +12808,16 @@
         <v>228</v>
       </c>
       <c r="J66" s="6" t="n">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.4653061224489796</v>
+        <v>0.474012474012474</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>-1.51</v>
+        <v>-1.33</v>
       </c>
       <c r="M66" s="10" t="n">
-        <v>2.9</v>
+        <v>2.74</v>
       </c>
       <c r="N66" s="10" t="n">
         <v>13.42</v>
@@ -12762,7 +12847,7 @@
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
@@ -12796,34 +12881,34 @@
         </is>
       </c>
       <c r="F67" s="7" t="n">
-        <v>1344800.21</v>
+        <v>1344802.18</v>
       </c>
       <c r="G67" s="7" t="n">
-        <v>1812850.36</v>
+        <v>1810613.31</v>
       </c>
       <c r="H67" s="8" t="n">
-        <v>1.34804437604899</v>
+        <v>1.346378922437499</v>
       </c>
       <c r="I67" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J67" s="6" t="n">
         <v>171</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8654970760233918</v>
       </c>
       <c r="L67" s="10" t="n">
         <v>-0.33</v>
       </c>
       <c r="M67" s="10" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="N67" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="O67" s="10" t="n">
-        <v>125.4692303007597</v>
+        <v>125.3142182058702</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -12847,7 +12932,7 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
@@ -12884,10 +12969,10 @@
         <v>102478.73</v>
       </c>
       <c r="G68" s="7" t="n">
-        <v>136717.01</v>
+        <v>136716.98</v>
       </c>
       <c r="H68" s="8" t="n">
-        <v>1.334101330100403</v>
+        <v>1.334101037356728</v>
       </c>
       <c r="I68" s="6" t="n">
         <v>2</v>
@@ -12905,10 +12990,10 @@
         <v>-0.71</v>
       </c>
       <c r="N68" s="10" t="n">
-        <v>-0.65</v>
+        <v>-0.64</v>
       </c>
       <c r="O68" s="10" t="n">
-        <v>124.171481299095</v>
+        <v>124.1714540519774</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -12932,7 +13017,7 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
@@ -12966,34 +13051,34 @@
         </is>
       </c>
       <c r="F69" s="7" t="n">
-        <v>550552.28</v>
+        <v>550934.48</v>
       </c>
       <c r="G69" s="7" t="n">
-        <v>706242.49</v>
+        <v>711573.35</v>
       </c>
       <c r="H69" s="8" t="n">
-        <v>1.282789147653698</v>
+        <v>1.291575270438692</v>
       </c>
       <c r="I69" s="6" t="n">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="J69" s="6" t="n">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.5585106382978723</v>
+        <v>0.6551724137931034</v>
       </c>
       <c r="L69" s="10" t="n">
-        <v>-1.39</v>
+        <v>-1.03</v>
       </c>
       <c r="M69" s="10" t="n">
-        <v>-2.85</v>
+        <v>-2.71</v>
       </c>
       <c r="N69" s="10" t="n">
-        <v>-2.13</v>
+        <v>-1.96</v>
       </c>
       <c r="O69" s="10" t="n">
-        <v>119.3955999178679</v>
+        <v>120.2133682960812</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -13017,7 +13102,7 @@
       </c>
       <c r="T69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U69" s="6" t="inlineStr">
@@ -13102,7 +13187,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -13136,34 +13221,34 @@
         </is>
       </c>
       <c r="F71" s="7" t="n">
-        <v>957294.62</v>
+        <v>959150.86</v>
       </c>
       <c r="G71" s="7" t="n">
-        <v>335030.89</v>
+        <v>335058.94</v>
       </c>
       <c r="H71" s="8" t="n">
-        <v>0.3499767814426869</v>
+        <v>0.3493287176951497</v>
       </c>
       <c r="I71" s="6" t="n">
         <v>9</v>
       </c>
       <c r="J71" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L71" s="10" t="n">
-        <v>-0.21</v>
+        <v>-0.02</v>
       </c>
       <c r="M71" s="10" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="N71" s="10" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="O71" s="10" t="n">
-        <v>108.5802964425936</v>
+        <v>108.3792346649202</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -13172,7 +13257,7 @@
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>Watch — thin / low activity</t>
+          <t>Tier 1 comparison</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13182,12 +13267,12 @@
       </c>
       <c r="S71" s="6" t="inlineStr">
         <is>
-          <t>below 500% growth screen</t>
+          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
         </is>
       </c>
       <c r="T71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U71" s="6" t="inlineStr">
@@ -13272,7 +13357,7 @@
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
@@ -13306,34 +13391,34 @@
         </is>
       </c>
       <c r="F73" s="7" t="n">
-        <v>218960.08</v>
+        <v>218946.44</v>
       </c>
       <c r="G73" s="7" t="n">
-        <v>1417451.36</v>
+        <v>1417483.59</v>
       </c>
       <c r="H73" s="8" t="n">
-        <v>6.473560660007067</v>
+        <v>6.474111157048272</v>
       </c>
       <c r="I73" s="6" t="n">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="J73" s="6" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.9691780821917808</v>
+        <v>0.9659863945578231</v>
       </c>
       <c r="L73" s="10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="M73" s="10" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="N73" s="10" t="n">
         <v>0.1</v>
       </c>
       <c r="O73" s="10" t="n">
-        <v>100.4211097383596</v>
+        <v>100.4296493237113</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -13357,7 +13442,7 @@
       </c>
       <c r="T73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U73" s="6" t="inlineStr">
@@ -13372,7 +13457,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>WALLET / WETH</t>
+          <t>WETH / WISHBONE</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -13382,7 +13467,7 @@
       </c>
       <c r="D74" s="6" t="inlineStr">
         <is>
-          <t>0x9501A20Bedb8beA0798FE5D4c411f5e270965D49</t>
+          <t>0x6Ec89bFF5E684C2561d0a88e185D8D4eb4b3AA30</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
@@ -13391,43 +13476,43 @@
         </is>
       </c>
       <c r="F74" s="7" t="n">
-        <v>2278849.27</v>
+        <v>99739.78999999999</v>
       </c>
       <c r="G74" s="7" t="n">
-        <v>696911.62</v>
+        <v>29956.06</v>
       </c>
       <c r="H74" s="8" t="n">
-        <v>0.3058173391169483</v>
+        <v>0.3003421202310533</v>
       </c>
       <c r="I74" s="6" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="J74" s="6" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.8048780487804879</v>
+        <v>0.6</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>5.89</v>
+        <v>5.23</v>
       </c>
       <c r="M74" s="10" t="n">
-        <v>6.48</v>
+        <v>5.07</v>
       </c>
       <c r="N74" s="10" t="n">
-        <v>24.52</v>
+        <v>-2.34</v>
       </c>
       <c r="O74" s="10" t="n">
-        <v>94.8798294610332</v>
+        <v>93.18114280168426</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 43.33% / 12h</t>
+          <t>Aggressive 122.5% / 12h</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Watch — thin / low activity</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13437,12 +13522,12 @@
       </c>
       <c r="S74" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
+          <t>below 500% growth screen</t>
         </is>
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U74" s="6" t="inlineStr">
@@ -13457,7 +13542,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>WETH / WISHBONE</t>
+          <t>WALLET / WETH</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -13467,7 +13552,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>0x6Ec89bFF5E684C2561d0a88e185D8D4eb4b3AA30</t>
+          <t>0x9501A20Bedb8beA0798FE5D4c411f5e270965D49</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -13476,43 +13561,43 @@
         </is>
       </c>
       <c r="F75" s="7" t="n">
-        <v>99433.56</v>
+        <v>2282878.99</v>
       </c>
       <c r="G75" s="7" t="n">
-        <v>29913.86</v>
+        <v>675280.51</v>
       </c>
       <c r="H75" s="8" t="n">
-        <v>0.3008426933522244</v>
+        <v>0.2958021484967103</v>
       </c>
       <c r="I75" s="6" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J75" s="6" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.631578947368421</v>
+        <v>0.9</v>
       </c>
       <c r="L75" s="10" t="n">
-        <v>4.84</v>
+        <v>6.04</v>
       </c>
       <c r="M75" s="10" t="n">
-        <v>4.68</v>
+        <v>6.48</v>
       </c>
       <c r="N75" s="10" t="n">
-        <v>-2.71</v>
+        <v>24.25</v>
       </c>
       <c r="O75" s="10" t="n">
-        <v>93.3364456125276</v>
+        <v>91.77261657110436</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 122.5% / 12h</t>
+          <t>Aggressive 43.33% / 12h</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>Watch — thin / low activity</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -13522,12 +13607,12 @@
       </c>
       <c r="S75" s="6" t="inlineStr">
         <is>
-          <t>below 500% growth screen</t>
+          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
         </is>
       </c>
       <c r="T75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U75" s="6" t="inlineStr">
@@ -13612,7 +13697,7 @@
       </c>
       <c r="T76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U76" s="6" t="inlineStr">
@@ -13649,10 +13734,10 @@
         <v>88995.48</v>
       </c>
       <c r="G77" s="7" t="n">
-        <v>84494.03</v>
+        <v>84123.03</v>
       </c>
       <c r="H77" s="8" t="n">
-        <v>0.9494193412968839</v>
+        <v>0.9452505902546962</v>
       </c>
       <c r="I77" s="6" t="n">
         <v>13</v>
@@ -13673,7 +13758,7 @@
         <v>-3.95</v>
       </c>
       <c r="O77" s="10" t="n">
-        <v>88.36720519120746</v>
+        <v>87.97919868795586</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -13697,7 +13782,7 @@
       </c>
       <c r="T77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U77" s="6" t="inlineStr">
@@ -13731,13 +13816,13 @@
         </is>
       </c>
       <c r="F78" s="7" t="n">
-        <v>304250.64</v>
+        <v>304845.23</v>
       </c>
       <c r="G78" s="7" t="n">
-        <v>281928.27</v>
+        <v>281928.8</v>
       </c>
       <c r="H78" s="8" t="n">
-        <v>0.9266316415965469</v>
+        <v>0.9248260174515442</v>
       </c>
       <c r="I78" s="6" t="n">
         <v>56</v>
@@ -13749,16 +13834,16 @@
         <v>0.6511627906976745</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>-0.73</v>
+        <v>-0.87</v>
       </c>
       <c r="M78" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N78" s="10" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O78" s="10" t="n">
-        <v>86.24624004159861</v>
+        <v>86.07818157430248</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -13782,7 +13867,7 @@
       </c>
       <c r="T78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U78" s="6" t="inlineStr">
@@ -13816,22 +13901,22 @@
         </is>
       </c>
       <c r="F79" s="7" t="n">
-        <v>740627.9300000001</v>
+        <v>740629.83</v>
       </c>
       <c r="G79" s="7" t="n">
-        <v>679266.0699999999</v>
+        <v>679330.22</v>
       </c>
       <c r="H79" s="8" t="n">
-        <v>0.9171488712287692</v>
+        <v>0.9172331338585161</v>
       </c>
       <c r="I79" s="6" t="n">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J79" s="6" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.9293478260869565</v>
+        <v>0.9346049046321526</v>
       </c>
       <c r="L79" s="10" t="n">
         <v>-0.06</v>
@@ -13843,7 +13928,7 @@
         <v>4.14</v>
       </c>
       <c r="O79" s="10" t="n">
-        <v>85.36363118961769</v>
+        <v>85.37147393388138</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -13867,7 +13952,7 @@
       </c>
       <c r="T79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U79" s="6" t="inlineStr">
@@ -13882,7 +13967,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>GLXY / USDG</t>
+          <t>WETH / PONS</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -13892,67 +13977,67 @@
       </c>
       <c r="D80" s="6" t="inlineStr">
         <is>
-          <t>0xC67C2D200E0b7E5D99F4CFBede8CB09B48892f2c</t>
+          <t>0xEd50bDeeA8aDC232f159486192a4157281D722ff</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>stocks</t>
+          <t>meme</t>
         </is>
       </c>
       <c r="F80" s="7" t="n">
-        <v>159612.78</v>
+        <v>6001307.55</v>
       </c>
       <c r="G80" s="7" t="n">
-        <v>142197.38</v>
+        <v>5348113.7</v>
       </c>
       <c r="H80" s="8" t="n">
-        <v>0.8908896894095824</v>
+        <v>0.8911580777092486</v>
       </c>
       <c r="I80" s="6" t="n">
-        <v>22</v>
+        <v>261</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>15</v>
+        <v>312</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.8365384615384616</v>
       </c>
       <c r="L80" s="10" t="n">
-        <v>-2.21</v>
+        <v>-0.27</v>
       </c>
       <c r="M80" s="10" t="n">
-        <v>-4.17</v>
+        <v>-1.7</v>
       </c>
       <c r="N80" s="10" t="n">
-        <v>-3.97</v>
+        <v>3.39</v>
       </c>
       <c r="O80" s="10" t="n">
-        <v>82.91955784179689</v>
+        <v>82.94453808278833</v>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 16.88% / 2h</t>
+          <t>Aggressive 30.21% / 8h</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>Watch — thin / low activity</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="S80" s="6" t="inlineStr">
         <is>
-          <t>below 500% growth screen</t>
+          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
         </is>
       </c>
       <c r="T80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U80" s="6" t="inlineStr">
@@ -13967,7 +14052,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>WETH / PONS</t>
+          <t>GLXY / USDG</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -13977,67 +14062,67 @@
       </c>
       <c r="D81" s="6" t="inlineStr">
         <is>
-          <t>0xEd50bDeeA8aDC232f159486192a4157281D722ff</t>
+          <t>0xC67C2D200E0b7E5D99F4CFBede8CB09B48892f2c</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>meme</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="F81" s="7" t="n">
-        <v>5996224.34</v>
+        <v>159612.78</v>
       </c>
       <c r="G81" s="7" t="n">
-        <v>5341727.21</v>
+        <v>142197.38</v>
       </c>
       <c r="H81" s="8" t="n">
-        <v>0.8908484584817919</v>
+        <v>0.8908896894095824</v>
       </c>
       <c r="I81" s="6" t="n">
-        <v>240</v>
+        <v>22</v>
       </c>
       <c r="J81" s="6" t="n">
-        <v>339</v>
+        <v>15</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.7079646017699115</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="L81" s="10" t="n">
-        <v>-0.53</v>
+        <v>-2.21</v>
       </c>
       <c r="M81" s="10" t="n">
-        <v>-1.82</v>
+        <v>-4.21</v>
       </c>
       <c r="N81" s="10" t="n">
-        <v>3.22</v>
+        <v>-3.97</v>
       </c>
       <c r="O81" s="10" t="n">
-        <v>82.91572027319279</v>
+        <v>82.91955784179689</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
-          <t>Aggressive 30.21% / 8h</t>
+          <t>Aggressive 16.88% / 2h</t>
         </is>
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Watch — thin / low activity</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S81" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison / parking candidate — below 500% growth screen</t>
+          <t>below 500% growth screen</t>
         </is>
       </c>
       <c r="T81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U81" s="6" t="inlineStr">
@@ -14122,7 +14207,7 @@
       </c>
       <c r="T82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U82" s="6" t="inlineStr">
@@ -14207,7 +14292,7 @@
       </c>
       <c r="T83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U83" s="6" t="inlineStr">
@@ -14292,7 +14377,7 @@
       </c>
       <c r="T84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U84" s="6" t="inlineStr">
@@ -14326,34 +14411,34 @@
         </is>
       </c>
       <c r="F85" s="7" t="n">
-        <v>1116959.31</v>
+        <v>1116812.62</v>
       </c>
       <c r="G85" s="7" t="n">
-        <v>267586.13</v>
+        <v>267590.98</v>
       </c>
       <c r="H85" s="8" t="n">
-        <v>0.2395665872555375</v>
+        <v>0.2396023963267893</v>
       </c>
       <c r="I85" s="6" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J85" s="6" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.8347107438016529</v>
+        <v>0.8114754098360656</v>
       </c>
       <c r="L85" s="10" t="n">
-        <v>-0.74</v>
+        <v>-0.77</v>
       </c>
       <c r="M85" s="10" t="n">
-        <v>-1.93</v>
+        <v>-1.99</v>
       </c>
       <c r="N85" s="10" t="n">
-        <v>-3.48</v>
+        <v>-3.51</v>
       </c>
       <c r="O85" s="10" t="n">
-        <v>74.3255336960305</v>
+        <v>74.33664346038638</v>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
@@ -14377,7 +14462,7 @@
       </c>
       <c r="T85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U85" s="6" t="inlineStr">
@@ -14414,10 +14499,10 @@
         <v>666075.37</v>
       </c>
       <c r="G86" s="7" t="n">
-        <v>158398.69</v>
+        <v>154546.75</v>
       </c>
       <c r="H86" s="8" t="n">
-        <v>0.2378089584666672</v>
+        <v>0.2320259192289305</v>
       </c>
       <c r="I86" s="6" t="n">
         <v>0</v>
@@ -14435,10 +14520,10 @@
         <v>-1.74</v>
       </c>
       <c r="N86" s="10" t="n">
-        <v>-0.78</v>
+        <v>-0.65</v>
       </c>
       <c r="O86" s="10" t="n">
-        <v>73.7802293642835</v>
+        <v>71.98604144077568</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -14462,7 +14547,7 @@
       </c>
       <c r="T86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U86" s="6" t="inlineStr">
@@ -14547,7 +14632,7 @@
       </c>
       <c r="T87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U87" s="6" t="inlineStr">
@@ -14632,7 +14717,7 @@
       </c>
       <c r="T88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U88" s="6" t="inlineStr">
@@ -14669,10 +14754,10 @@
         <v>393856.93</v>
       </c>
       <c r="G89" s="7" t="n">
-        <v>86424.33</v>
+        <v>86420.66</v>
       </c>
       <c r="H89" s="8" t="n">
-        <v>0.219430771473286</v>
+        <v>0.2194214533688667</v>
       </c>
       <c r="I89" s="6" t="n">
         <v>7</v>
@@ -14690,10 +14775,10 @@
         <v>0.46</v>
       </c>
       <c r="N89" s="10" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O89" s="10" t="n">
-        <v>68.07839684958698</v>
+        <v>68.0755059076909</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
@@ -14717,7 +14802,7 @@
       </c>
       <c r="T89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U89" s="6" t="inlineStr">
@@ -14802,7 +14887,7 @@
       </c>
       <c r="T90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U90" s="6" t="inlineStr">
@@ -14887,7 +14972,7 @@
       </c>
       <c r="T91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U91" s="6" t="inlineStr">
@@ -14921,34 +15006,34 @@
         </is>
       </c>
       <c r="F92" s="7" t="n">
-        <v>19009107.46</v>
+        <v>19007528.26</v>
       </c>
       <c r="G92" s="7" t="n">
-        <v>400309023.8</v>
+        <v>400093412.34</v>
       </c>
       <c r="H92" s="8" t="n">
-        <v>21.05880166348431</v>
+        <v>21.04920781214716</v>
       </c>
       <c r="I92" s="6" t="n">
-        <v>13680</v>
+        <v>13657</v>
       </c>
       <c r="J92" s="6" t="n">
-        <v>13026</v>
+        <v>13010</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.9521929824561404</v>
+        <v>0.9526250274584462</v>
       </c>
       <c r="L92" s="10" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="M92" s="10" t="n">
         <v>0.06</v>
       </c>
       <c r="N92" s="10" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="O92" s="10" t="n">
-        <v>65.33493216096007</v>
+        <v>65.30516723718657</v>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
@@ -14972,7 +15057,7 @@
       </c>
       <c r="T92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U92" s="6" t="inlineStr">
@@ -15057,7 +15142,7 @@
       </c>
       <c r="T93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U93" s="6" t="inlineStr">
@@ -15091,34 +15176,34 @@
         </is>
       </c>
       <c r="F94" s="7" t="n">
-        <v>4706469.87</v>
+        <v>4706340.24</v>
       </c>
       <c r="G94" s="7" t="n">
-        <v>19510297.65</v>
+        <v>19507603.76</v>
       </c>
       <c r="H94" s="8" t="n">
-        <v>4.145420705731619</v>
+        <v>4.14496249000476</v>
       </c>
       <c r="I94" s="6" t="n">
         <v>1652</v>
       </c>
       <c r="J94" s="6" t="n">
-        <v>1509</v>
+        <v>1512</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.9134382566585957</v>
+        <v>0.9152542372881356</v>
       </c>
       <c r="L94" s="10" t="n">
-        <v>-0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="M94" s="10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="N94" s="10" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O94" s="10" t="n">
-        <v>64.30583869766173</v>
+        <v>64.29873062619885</v>
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
@@ -15142,7 +15227,7 @@
       </c>
       <c r="T94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U94" s="6" t="inlineStr">
@@ -15176,13 +15261,13 @@
         </is>
       </c>
       <c r="F95" s="7" t="n">
-        <v>1551729.91</v>
+        <v>1552229.25</v>
       </c>
       <c r="G95" s="7" t="n">
         <v>1067033.81</v>
       </c>
       <c r="H95" s="8" t="n">
-        <v>0.687641453015493</v>
+        <v>0.6874202441424165</v>
       </c>
       <c r="I95" s="6" t="n">
         <v>76</v>
@@ -15203,7 +15288,7 @@
         <v>1.22</v>
       </c>
       <c r="O95" s="10" t="n">
-        <v>64.00222823941701</v>
+        <v>63.98163922355541</v>
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
@@ -15227,7 +15312,7 @@
       </c>
       <c r="T95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U95" s="6" t="inlineStr">
@@ -15273,13 +15358,13 @@
         <v>19</v>
       </c>
       <c r="J96" s="6" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.3584905660377358</v>
+        <v>0.3653846153846154</v>
       </c>
       <c r="L96" s="10" t="n">
-        <v>-0.47</v>
+        <v>-0.8</v>
       </c>
       <c r="M96" s="10" t="n">
         <v>-2.16</v>
@@ -15312,7 +15397,7 @@
       </c>
       <c r="T96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U96" s="6" t="inlineStr">
@@ -15349,31 +15434,31 @@
         <v>161134.3</v>
       </c>
       <c r="G97" s="7" t="n">
-        <v>106878.71</v>
+        <v>106740.63</v>
       </c>
       <c r="H97" s="8" t="n">
-        <v>0.6632896285893197</v>
+        <v>0.6624327036515504</v>
       </c>
       <c r="I97" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J97" s="6" t="n">
         <v>27</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.1851851851851852</v>
       </c>
       <c r="L97" s="10" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="M97" s="10" t="n">
         <v>-1.95</v>
       </c>
       <c r="N97" s="10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="O97" s="10" t="n">
-        <v>61.73568218095092</v>
+        <v>61.65592389236805</v>
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
@@ -15397,7 +15482,7 @@
       </c>
       <c r="T97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U97" s="6" t="inlineStr">
@@ -15482,7 +15567,7 @@
       </c>
       <c r="T98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U98" s="6" t="inlineStr">
@@ -15537,7 +15622,7 @@
         <v>-0.7</v>
       </c>
       <c r="M99" s="10" t="n">
-        <v>-0.7</v>
+        <v>-0.73</v>
       </c>
       <c r="N99" s="10" t="n">
         <v>0.83</v>
@@ -15567,7 +15652,7 @@
       </c>
       <c r="T99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U99" s="6" t="inlineStr">
@@ -15652,7 +15737,7 @@
       </c>
       <c r="T100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U100" s="6" t="inlineStr">
@@ -15689,22 +15774,22 @@
         <v>133762.71</v>
       </c>
       <c r="G101" s="7" t="n">
-        <v>85055.95</v>
+        <v>85033.64</v>
       </c>
       <c r="H101" s="8" t="n">
-        <v>0.6358719107888888</v>
+        <v>0.6357051229000967</v>
       </c>
       <c r="I101" s="6" t="n">
         <v>0</v>
       </c>
       <c r="J101" s="6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="L101" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.41</v>
       </c>
       <c r="M101" s="10" t="n">
         <v>0.21</v>
@@ -15713,7 +15798,7 @@
         <v>2.02</v>
       </c>
       <c r="O101" s="10" t="n">
-        <v>59.18377809667582</v>
+        <v>59.16825431392652</v>
       </c>
       <c r="P101" s="6" t="inlineStr">
         <is>
@@ -15737,7 +15822,7 @@
       </c>
       <c r="T101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U101" s="6" t="inlineStr">
@@ -15822,7 +15907,7 @@
       </c>
       <c r="T102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U102" s="6" t="inlineStr">
@@ -15856,34 +15941,34 @@
         </is>
       </c>
       <c r="F103" s="7" t="n">
-        <v>998463.46</v>
+        <v>998492.49</v>
       </c>
       <c r="G103" s="7" t="n">
-        <v>3729429.27</v>
+        <v>3723276.88</v>
       </c>
       <c r="H103" s="8" t="n">
-        <v>3.735168505815927</v>
+        <v>3.728898231372777</v>
       </c>
       <c r="I103" s="6" t="n">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J103" s="6" t="n">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.9434889434889435</v>
+        <v>0.9578163771712159</v>
       </c>
       <c r="L103" s="10" t="n">
-        <v>-1.09</v>
+        <v>-1.05</v>
       </c>
       <c r="M103" s="10" t="n">
-        <v>-1.42</v>
+        <v>-1.57</v>
       </c>
       <c r="N103" s="10" t="n">
-        <v>-0.25</v>
+        <v>-0.17</v>
       </c>
       <c r="O103" s="10" t="n">
-        <v>57.94180144646957</v>
+        <v>57.8445338141702</v>
       </c>
       <c r="P103" s="6" t="inlineStr">
         <is>
@@ -15907,7 +15992,7 @@
       </c>
       <c r="T103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U103" s="6" t="inlineStr">
@@ -15941,34 +16026,34 @@
         </is>
       </c>
       <c r="F104" s="7" t="n">
-        <v>2536305.53</v>
+        <v>2536636.13</v>
       </c>
       <c r="G104" s="7" t="n">
-        <v>9398407.98</v>
+        <v>9380693.859999999</v>
       </c>
       <c r="H104" s="8" t="n">
-        <v>3.705550403464208</v>
+        <v>3.6980841473704</v>
       </c>
       <c r="I104" s="6" t="n">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J104" s="6" t="n">
         <v>444</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.7184684684684685</v>
+        <v>0.7274774774774775</v>
       </c>
       <c r="L104" s="10" t="n">
-        <v>-0.82</v>
+        <v>-0.79</v>
       </c>
       <c r="M104" s="10" t="n">
-        <v>-1.56</v>
+        <v>-1.54</v>
       </c>
       <c r="N104" s="10" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O104" s="10" t="n">
-        <v>57.48235063373852</v>
+        <v>57.36653033608332</v>
       </c>
       <c r="P104" s="6" t="inlineStr">
         <is>
@@ -15992,7 +16077,7 @@
       </c>
       <c r="T104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U104" s="6" t="inlineStr">
@@ -16077,7 +16162,7 @@
       </c>
       <c r="T105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U105" s="6" t="inlineStr">
@@ -16114,22 +16199,22 @@
         <v>479211.98</v>
       </c>
       <c r="G106" s="7" t="n">
-        <v>291057.32</v>
+        <v>289567.53</v>
       </c>
       <c r="H106" s="8" t="n">
-        <v>0.6073665353691701</v>
+        <v>0.6042577024055201</v>
       </c>
       <c r="I106" s="6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J106" s="6" t="n">
         <v>17</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>0.7391304347826086</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="L106" s="10" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="M106" s="10" t="n">
         <v>-1.42</v>
@@ -16138,7 +16223,7 @@
         <v>4.47</v>
       </c>
       <c r="O106" s="10" t="n">
-        <v>56.5306402794855</v>
+        <v>56.24128565139378</v>
       </c>
       <c r="P106" s="6" t="inlineStr">
         <is>
@@ -16162,7 +16247,7 @@
       </c>
       <c r="T106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U106" s="6" t="inlineStr">
@@ -16196,22 +16281,22 @@
         </is>
       </c>
       <c r="F107" s="7" t="n">
-        <v>1132694.64</v>
+        <v>1132694.94</v>
       </c>
       <c r="G107" s="7" t="n">
-        <v>205181.46</v>
+        <v>205184.46</v>
       </c>
       <c r="H107" s="8" t="n">
-        <v>0.1811445492493899</v>
+        <v>0.1811471498230583</v>
       </c>
       <c r="I107" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J107" s="6" t="n">
         <v>24</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.375</v>
+        <v>0.4166666666666667</v>
       </c>
       <c r="L107" s="10" t="n">
         <v>-0.17</v>
@@ -16223,7 +16308,7 @@
         <v>0.92</v>
       </c>
       <c r="O107" s="10" t="n">
-        <v>56.20009640462323</v>
+        <v>56.20090323260383</v>
       </c>
       <c r="P107" s="6" t="inlineStr">
         <is>
@@ -16232,7 +16317,7 @@
       </c>
       <c r="Q107" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 comparison</t>
+          <t>Tier 1</t>
         </is>
       </c>
       <c r="R107" s="6" t="inlineStr">
@@ -16247,7 +16332,7 @@
       </c>
       <c r="T107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U107" s="6" t="inlineStr">
@@ -16284,10 +16369,10 @@
         <v>214102.43</v>
       </c>
       <c r="G108" s="7" t="n">
-        <v>127022.16</v>
+        <v>126880.75</v>
       </c>
       <c r="H108" s="8" t="n">
-        <v>0.5932775260887978</v>
+        <v>0.5926170478307976</v>
       </c>
       <c r="I108" s="6" t="n">
         <v>5</v>
@@ -16305,10 +16390,10 @@
         <v>-2.34</v>
       </c>
       <c r="N108" s="10" t="n">
-        <v>-3.95</v>
+        <v>-3.93</v>
       </c>
       <c r="O108" s="10" t="n">
-        <v>55.21930574071485</v>
+        <v>55.15783172685149</v>
       </c>
       <c r="P108" s="6" t="inlineStr">
         <is>
@@ -16332,7 +16417,7 @@
       </c>
       <c r="T108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U108" s="6" t="inlineStr">
@@ -16417,7 +16502,7 @@
       </c>
       <c r="T109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U109" s="6" t="inlineStr">
@@ -16502,7 +16587,7 @@
       </c>
       <c r="T110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U110" s="6" t="inlineStr">
@@ -16536,13 +16621,13 @@
         </is>
       </c>
       <c r="F111" s="7" t="n">
-        <v>474482.4</v>
+        <v>474488.54</v>
       </c>
       <c r="G111" s="7" t="n">
-        <v>1609952.96</v>
+        <v>1608835.49</v>
       </c>
       <c r="H111" s="8" t="n">
-        <v>3.393072029647464</v>
+        <v>3.390673018151292</v>
       </c>
       <c r="I111" s="6" t="n">
         <v>122</v>
@@ -16560,10 +16645,10 @@
         <v>0.32</v>
       </c>
       <c r="N111" s="10" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="O111" s="10" t="n">
-        <v>52.63502985990629</v>
+        <v>52.59781519407192</v>
       </c>
       <c r="P111" s="6" t="inlineStr">
         <is>
@@ -16587,7 +16672,7 @@
       </c>
       <c r="T111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U111" s="6" t="inlineStr">
@@ -16624,10 +16709,10 @@
         <v>70492.31</v>
       </c>
       <c r="G112" s="7" t="n">
-        <v>39319.47</v>
+        <v>39319.44</v>
       </c>
       <c r="H112" s="8" t="n">
-        <v>0.5577838206749077</v>
+        <v>0.5577833950965716</v>
       </c>
       <c r="I112" s="6" t="n">
         <v>3</v>
@@ -16642,13 +16727,13 @@
         <v>-0.5600000000000001</v>
       </c>
       <c r="M112" s="10" t="n">
-        <v>-2.87</v>
+        <v>-2.98</v>
       </c>
       <c r="N112" s="10" t="n">
-        <v>-1.6</v>
+        <v>-1.57</v>
       </c>
       <c r="O112" s="10" t="n">
-        <v>51.91572910931702</v>
+        <v>51.9156894986134</v>
       </c>
       <c r="P112" s="6" t="inlineStr">
         <is>
@@ -16672,7 +16757,7 @@
       </c>
       <c r="T112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U112" s="6" t="inlineStr">
@@ -16757,7 +16842,7 @@
       </c>
       <c r="T113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U113" s="6" t="inlineStr">
@@ -16794,10 +16879,10 @@
         <v>3295091.66</v>
       </c>
       <c r="G114" s="7" t="n">
-        <v>1709069.37</v>
+        <v>1708860.65</v>
       </c>
       <c r="H114" s="8" t="n">
-        <v>0.5186712681613234</v>
+        <v>0.5186079254620795</v>
       </c>
       <c r="I114" s="6" t="n">
         <v>3</v>
@@ -16812,13 +16897,13 @@
         <v>-1.32</v>
       </c>
       <c r="M114" s="10" t="n">
-        <v>3.53</v>
+        <v>3.42</v>
       </c>
       <c r="N114" s="10" t="n">
-        <v>4.54</v>
+        <v>4.53</v>
       </c>
       <c r="O114" s="10" t="n">
-        <v>48.27532828411517</v>
+        <v>48.26943266238305</v>
       </c>
       <c r="P114" s="6" t="inlineStr">
         <is>
@@ -16842,7 +16927,7 @@
       </c>
       <c r="T114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U114" s="6" t="inlineStr">
@@ -16927,7 +17012,7 @@
       </c>
       <c r="T115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U115" s="6" t="inlineStr">
@@ -17012,7 +17097,7 @@
       </c>
       <c r="T116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U116" s="6" t="inlineStr">
@@ -17097,7 +17182,7 @@
       </c>
       <c r="T117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U117" s="6" t="inlineStr">
@@ -17182,7 +17267,7 @@
       </c>
       <c r="T118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U118" s="6" t="inlineStr">
@@ -17267,7 +17352,7 @@
       </c>
       <c r="T119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U119" s="6" t="inlineStr">
@@ -17301,34 +17386,34 @@
         </is>
       </c>
       <c r="F120" s="7" t="n">
-        <v>329924.4</v>
+        <v>330071.28</v>
       </c>
       <c r="G120" s="7" t="n">
-        <v>925105.77</v>
+        <v>928580.63</v>
       </c>
       <c r="H120" s="8" t="n">
-        <v>2.803993187530234</v>
+        <v>2.813273029995218</v>
       </c>
       <c r="I120" s="6" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J120" s="6" t="n">
         <v>50</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.92</v>
+        <v>0.98</v>
       </c>
       <c r="L120" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.76</v>
       </c>
       <c r="M120" s="10" t="n">
-        <v>-1.84</v>
+        <v>-1.77</v>
       </c>
       <c r="N120" s="10" t="n">
-        <v>-2.31</v>
+        <v>-2.22</v>
       </c>
       <c r="O120" s="10" t="n">
-        <v>43.49694432156275</v>
+        <v>43.64089787780082</v>
       </c>
       <c r="P120" s="6" t="inlineStr">
         <is>
@@ -17352,7 +17437,7 @@
       </c>
       <c r="T120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U120" s="6" t="inlineStr">
@@ -17386,34 +17471,34 @@
         </is>
       </c>
       <c r="F121" s="7" t="n">
-        <v>22006.1</v>
+        <v>22045.14</v>
       </c>
       <c r="G121" s="7" t="n">
-        <v>3081.73</v>
+        <v>3083.58</v>
       </c>
       <c r="H121" s="8" t="n">
-        <v>0.1400398071443827</v>
+        <v>0.1398757277114139</v>
       </c>
       <c r="I121" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J121" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.25</v>
       </c>
       <c r="L121" s="10" t="n">
-        <v>-4.99</v>
+        <v>-4.83</v>
       </c>
       <c r="M121" s="10" t="n">
-        <v>-6.32</v>
+        <v>-6.17</v>
       </c>
       <c r="N121" s="10" t="n">
-        <v>-8.529999999999999</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="O121" s="10" t="n">
-        <v>43.44735016654474</v>
+        <v>43.39644452246618</v>
       </c>
       <c r="P121" s="6" t="inlineStr">
         <is>
@@ -17437,7 +17522,7 @@
       </c>
       <c r="T121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U121" s="6" t="inlineStr">
@@ -17471,22 +17556,22 @@
         </is>
       </c>
       <c r="F122" s="7" t="n">
-        <v>131427.81</v>
+        <v>131428.22</v>
       </c>
       <c r="G122" s="7" t="n">
-        <v>60588.03</v>
+        <v>60597.78</v>
       </c>
       <c r="H122" s="8" t="n">
-        <v>0.4609985512198674</v>
+        <v>0.4610712980819492</v>
       </c>
       <c r="I122" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J122" s="6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="L122" s="10" t="n">
         <v>-0.36</v>
@@ -17498,7 +17583,7 @@
         <v>-0.34</v>
       </c>
       <c r="O122" s="10" t="n">
-        <v>42.90744015478916</v>
+        <v>42.91421106897742</v>
       </c>
       <c r="P122" s="6" t="inlineStr">
         <is>
@@ -17522,7 +17607,7 @@
       </c>
       <c r="T122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U122" s="6" t="inlineStr">
@@ -17556,22 +17641,22 @@
         </is>
       </c>
       <c r="F123" s="7" t="n">
-        <v>830409.27</v>
+        <v>830409.26</v>
       </c>
       <c r="G123" s="7" t="n">
-        <v>381636.31</v>
+        <v>381639.59</v>
       </c>
       <c r="H123" s="8" t="n">
-        <v>0.4595761677853138</v>
+        <v>0.4595801231792623</v>
       </c>
       <c r="I123" s="6" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J123" s="6" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.3875</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="L123" s="10" t="n">
         <v>-0.2</v>
@@ -17583,7 +17668,7 @@
         <v>0.64</v>
       </c>
       <c r="O123" s="10" t="n">
-        <v>42.7750518166181</v>
+        <v>42.77541996490983</v>
       </c>
       <c r="P123" s="6" t="inlineStr">
         <is>
@@ -17607,7 +17692,7 @@
       </c>
       <c r="T123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U123" s="6" t="inlineStr">
@@ -17644,10 +17729,10 @@
         <v>8351126</v>
       </c>
       <c r="G124" s="7" t="n">
-        <v>1143590.73</v>
+        <v>1141092.91</v>
       </c>
       <c r="H124" s="8" t="n">
-        <v>0.1369385074539649</v>
+        <v>0.1366394076679001</v>
       </c>
       <c r="I124" s="6" t="n">
         <v>21</v>
@@ -17662,13 +17747,13 @@
         <v>-0.17</v>
       </c>
       <c r="M124" s="10" t="n">
-        <v>-0.79</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N124" s="10" t="n">
-        <v>-7.31</v>
+        <v>-7.23</v>
       </c>
       <c r="O124" s="10" t="n">
-        <v>42.48517193759261</v>
+        <v>42.39237622896601</v>
       </c>
       <c r="P124" s="6" t="inlineStr">
         <is>
@@ -17692,7 +17777,7 @@
       </c>
       <c r="T124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U124" s="6" t="inlineStr">
@@ -17726,34 +17811,34 @@
         </is>
       </c>
       <c r="F125" s="7" t="n">
-        <v>962972.14</v>
+        <v>962491.15</v>
       </c>
       <c r="G125" s="7" t="n">
-        <v>2599450.63</v>
+        <v>2603747.91</v>
       </c>
       <c r="H125" s="8" t="n">
-        <v>2.699403775066639</v>
+        <v>2.705217507714227</v>
       </c>
       <c r="I125" s="6" t="n">
         <v>236</v>
       </c>
       <c r="J125" s="6" t="n">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.8581818181818182</v>
+        <v>0.8166089965397924</v>
       </c>
       <c r="L125" s="10" t="n">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="M125" s="10" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="N125" s="10" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="O125" s="10" t="n">
-        <v>41.87450106072123</v>
+        <v>41.96468658841695</v>
       </c>
       <c r="P125" s="6" t="inlineStr">
         <is>
@@ -17777,7 +17862,7 @@
       </c>
       <c r="T125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U125" s="6" t="inlineStr">
@@ -17814,10 +17899,10 @@
         <v>548261.9300000001</v>
       </c>
       <c r="G126" s="7" t="n">
-        <v>73763.00999999999</v>
+        <v>72386.00999999999</v>
       </c>
       <c r="H126" s="8" t="n">
-        <v>0.1345397262946927</v>
+        <v>0.1320281530399165</v>
       </c>
       <c r="I126" s="6" t="n">
         <v>1</v>
@@ -17835,10 +17920,10 @@
         <v>-1.43</v>
       </c>
       <c r="N126" s="10" t="n">
-        <v>-0.43</v>
+        <v>-0.41</v>
       </c>
       <c r="O126" s="10" t="n">
-        <v>41.74095008292842</v>
+        <v>40.96173448063409</v>
       </c>
       <c r="P126" s="6" t="inlineStr">
         <is>
@@ -17862,7 +17947,7 @@
       </c>
       <c r="T126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U126" s="6" t="inlineStr">
@@ -17947,7 +18032,7 @@
       </c>
       <c r="T127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U127" s="6" t="inlineStr">
@@ -17984,10 +18069,10 @@
         <v>51055.15</v>
       </c>
       <c r="G128" s="7" t="n">
-        <v>6582.55</v>
+        <v>6581.43</v>
       </c>
       <c r="H128" s="8" t="n">
-        <v>0.1289301862789552</v>
+        <v>0.1289082492167783</v>
       </c>
       <c r="I128" s="6" t="n">
         <v>1</v>
@@ -18005,10 +18090,10 @@
         <v>-2.83</v>
       </c>
       <c r="N128" s="10" t="n">
-        <v>-12.99</v>
+        <v>-12.88</v>
       </c>
       <c r="O128" s="10" t="n">
-        <v>40.00059029304585</v>
+        <v>39.99378431950548</v>
       </c>
       <c r="P128" s="6" t="inlineStr">
         <is>
@@ -18032,7 +18117,7 @@
       </c>
       <c r="T128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U128" s="6" t="inlineStr">
@@ -18117,7 +18202,7 @@
       </c>
       <c r="T129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U129" s="6" t="inlineStr">
@@ -18202,7 +18287,7 @@
       </c>
       <c r="T130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U130" s="6" t="inlineStr">
@@ -18287,7 +18372,7 @@
       </c>
       <c r="T131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U131" s="6" t="inlineStr">
@@ -18324,10 +18409,10 @@
         <v>125198.63</v>
       </c>
       <c r="G132" s="7" t="n">
-        <v>12651.16</v>
+        <v>12483.79</v>
       </c>
       <c r="H132" s="8" t="n">
-        <v>0.1010487095585631</v>
+        <v>0.09971187384398696</v>
       </c>
       <c r="I132" s="6" t="n">
         <v>0</v>
@@ -18345,10 +18430,10 @@
         <v>-0.2</v>
       </c>
       <c r="N132" s="10" t="n">
-        <v>-1.62</v>
+        <v>-1.69</v>
       </c>
       <c r="O132" s="10" t="n">
-        <v>31.35036214054418</v>
+        <v>30.93560886009695</v>
       </c>
       <c r="P132" s="6" t="inlineStr">
         <is>
@@ -18372,7 +18457,7 @@
       </c>
       <c r="T132" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U132" s="6" t="inlineStr">
@@ -18457,7 +18542,7 @@
       </c>
       <c r="T133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U133" s="6" t="inlineStr">
@@ -18542,7 +18627,7 @@
       </c>
       <c r="T134" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U134" s="6" t="inlineStr">
@@ -18627,7 +18712,7 @@
       </c>
       <c r="T135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U135" s="6" t="inlineStr">
@@ -18712,7 +18797,7 @@
       </c>
       <c r="T136" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U136" s="6" t="inlineStr">
@@ -18797,7 +18882,7 @@
       </c>
       <c r="T137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U137" s="6" t="inlineStr">
@@ -18834,19 +18919,19 @@
         <v>363260.97</v>
       </c>
       <c r="G138" s="7" t="n">
-        <v>562407.62</v>
+        <v>560353.84</v>
       </c>
       <c r="H138" s="8" t="n">
-        <v>1.54821923203035</v>
+        <v>1.542565500499544</v>
       </c>
       <c r="I138" s="6" t="n">
         <v>48</v>
       </c>
       <c r="J138" s="6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.8135593220338984</v>
+        <v>0.8275862068965517</v>
       </c>
       <c r="L138" s="10" t="n">
         <v>-0.2</v>
@@ -18855,10 +18940,10 @@
         <v>-0.22</v>
       </c>
       <c r="N138" s="10" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
       <c r="O138" s="10" t="n">
-        <v>24.01675083687081</v>
+        <v>23.92904732649918</v>
       </c>
       <c r="P138" s="6" t="inlineStr">
         <is>
@@ -18882,7 +18967,7 @@
       </c>
       <c r="T138" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U138" s="6" t="inlineStr">
@@ -18967,7 +19052,7 @@
       </c>
       <c r="T139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U139" s="6" t="inlineStr">
@@ -19052,7 +19137,7 @@
       </c>
       <c r="T140" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U140" s="6" t="inlineStr">
@@ -19086,34 +19171,34 @@
         </is>
       </c>
       <c r="F141" s="7" t="n">
-        <v>1344800.21</v>
+        <v>1344802.18</v>
       </c>
       <c r="G141" s="7" t="n">
-        <v>1812850.36</v>
+        <v>1810613.31</v>
       </c>
       <c r="H141" s="8" t="n">
-        <v>1.34804437604899</v>
+        <v>1.346378922437499</v>
       </c>
       <c r="I141" s="6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J141" s="6" t="n">
         <v>171</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8654970760233918</v>
       </c>
       <c r="L141" s="10" t="n">
         <v>-0.33</v>
       </c>
       <c r="M141" s="10" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="N141" s="10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="O141" s="10" t="n">
-        <v>20.91153838345995</v>
+        <v>20.88570303431171</v>
       </c>
       <c r="P141" s="6" t="inlineStr">
         <is>
@@ -19137,7 +19222,7 @@
       </c>
       <c r="T141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U141" s="6" t="inlineStr">
@@ -19174,10 +19259,10 @@
         <v>879629.22</v>
       </c>
       <c r="G142" s="7" t="n">
-        <v>53530.94</v>
+        <v>53496.06</v>
       </c>
       <c r="H142" s="8" t="n">
-        <v>0.0608562548661128</v>
+        <v>0.06081660179501541</v>
       </c>
       <c r="I142" s="6" t="n">
         <v>7</v>
@@ -19195,10 +19280,10 @@
         <v>3.33</v>
       </c>
       <c r="N142" s="10" t="n">
-        <v>5.93</v>
+        <v>5.72</v>
       </c>
       <c r="O142" s="10" t="n">
-        <v>18.88065307221149</v>
+        <v>18.86835070690353</v>
       </c>
       <c r="P142" s="6" t="inlineStr">
         <is>
@@ -19222,7 +19307,7 @@
       </c>
       <c r="T142" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U142" s="6" t="inlineStr">
@@ -19307,7 +19392,7 @@
       </c>
       <c r="T143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U143" s="6" t="inlineStr">
@@ -19392,7 +19477,7 @@
       </c>
       <c r="T144" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U144" s="6" t="inlineStr">
@@ -19435,16 +19520,16 @@
         <v>0.05350656346844922</v>
       </c>
       <c r="I145" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J145" s="6" t="n">
         <v>4</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L145" s="10" t="n">
-        <v>0.62</v>
+        <v>-0.02</v>
       </c>
       <c r="M145" s="10" t="n">
         <v>1.9</v>
@@ -19477,7 +19562,7 @@
       </c>
       <c r="T145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U145" s="6" t="inlineStr">
@@ -19562,7 +19647,7 @@
       </c>
       <c r="T146" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U146" s="6" t="inlineStr">
@@ -19647,7 +19732,7 @@
       </c>
       <c r="T147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U147" s="6" t="inlineStr">
@@ -19681,13 +19766,13 @@
         </is>
       </c>
       <c r="F148" s="7" t="n">
-        <v>304250.64</v>
+        <v>304845.23</v>
       </c>
       <c r="G148" s="7" t="n">
-        <v>281928.27</v>
+        <v>281928.8</v>
       </c>
       <c r="H148" s="8" t="n">
-        <v>0.9266316415965469</v>
+        <v>0.9248260174515442</v>
       </c>
       <c r="I148" s="6" t="n">
         <v>56</v>
@@ -19699,16 +19784,16 @@
         <v>0.6511627906976745</v>
       </c>
       <c r="L148" s="10" t="n">
-        <v>-0.73</v>
+        <v>-0.87</v>
       </c>
       <c r="M148" s="10" t="n">
-        <v>-0.88</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N148" s="10" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O148" s="10" t="n">
-        <v>14.37437334026643</v>
+        <v>14.34636359571708</v>
       </c>
       <c r="P148" s="6" t="inlineStr">
         <is>
@@ -19732,7 +19817,7 @@
       </c>
       <c r="T148" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U148" s="6" t="inlineStr">
@@ -19817,7 +19902,7 @@
       </c>
       <c r="T149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U149" s="6" t="inlineStr">
@@ -19854,10 +19939,10 @@
         <v>4692.14</v>
       </c>
       <c r="G150" s="7" t="n">
-        <v>3952.52</v>
+        <v>3946.24</v>
       </c>
       <c r="H150" s="8" t="n">
-        <v>0.842370432254792</v>
+        <v>0.8410320237674067</v>
       </c>
       <c r="I150" s="6" t="n">
         <v>11</v>
@@ -19878,7 +19963,7 @@
         <v>0.59</v>
       </c>
       <c r="O150" s="10" t="n">
-        <v>13.06727133035246</v>
+        <v>13.0465092686919</v>
       </c>
       <c r="P150" s="6" t="inlineStr">
         <is>
@@ -19902,7 +19987,7 @@
       </c>
       <c r="T150" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U150" s="6" t="inlineStr">
@@ -19987,7 +20072,7 @@
       </c>
       <c r="T151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U151" s="6" t="inlineStr">
@@ -20072,7 +20157,7 @@
       </c>
       <c r="T152" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U152" s="6" t="inlineStr">
@@ -20157,7 +20242,7 @@
       </c>
       <c r="T153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U153" s="6" t="inlineStr">
@@ -20242,7 +20327,7 @@
       </c>
       <c r="T154" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U154" s="6" t="inlineStr">
@@ -20327,7 +20412,7 @@
       </c>
       <c r="T155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U155" s="6" t="inlineStr">
@@ -20412,7 +20497,7 @@
       </c>
       <c r="T156" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U156" s="6" t="inlineStr">
@@ -20449,10 +20534,10 @@
         <v>125198.63</v>
       </c>
       <c r="G157" s="7" t="n">
-        <v>12651.16</v>
+        <v>12483.79</v>
       </c>
       <c r="H157" s="8" t="n">
-        <v>0.1010487095585631</v>
+        <v>0.09971187384398696</v>
       </c>
       <c r="I157" s="6" t="n">
         <v>0</v>
@@ -20470,10 +20555,10 @@
         <v>-0.2</v>
       </c>
       <c r="N157" s="10" t="n">
-        <v>-1.62</v>
+        <v>-1.69</v>
       </c>
       <c r="O157" s="10" t="n">
-        <v>9.405108642163256</v>
+        <v>9.280682658029086</v>
       </c>
       <c r="P157" s="6" t="inlineStr">
         <is>
@@ -20497,7 +20582,7 @@
       </c>
       <c r="T157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U157" s="6" t="inlineStr">
@@ -20582,7 +20667,7 @@
       </c>
       <c r="T158" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U158" s="6" t="inlineStr">
@@ -20667,7 +20752,7 @@
       </c>
       <c r="T159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U159" s="6" t="inlineStr">
@@ -20752,7 +20837,7 @@
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U160" s="6" t="inlineStr">
@@ -20789,10 +20874,10 @@
         <v>879629.22</v>
       </c>
       <c r="G161" s="7" t="n">
-        <v>53530.94</v>
+        <v>53496.06</v>
       </c>
       <c r="H161" s="8" t="n">
-        <v>0.0608562548661128</v>
+        <v>0.06081660179501541</v>
       </c>
       <c r="I161" s="6" t="n">
         <v>7</v>
@@ -20810,10 +20895,10 @@
         <v>3.33</v>
       </c>
       <c r="N161" s="10" t="n">
-        <v>5.93</v>
+        <v>5.72</v>
       </c>
       <c r="O161" s="10" t="n">
-        <v>5.664195921663449</v>
+        <v>5.660505212071059</v>
       </c>
       <c r="P161" s="6" t="inlineStr">
         <is>
@@ -20837,7 +20922,7 @@
       </c>
       <c r="T161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U161" s="6" t="inlineStr">
@@ -20874,10 +20959,10 @@
         <v>2398790.21</v>
       </c>
       <c r="G162" s="7" t="n">
-        <v>141343.06</v>
+        <v>141339.33</v>
       </c>
       <c r="H162" s="8" t="n">
-        <v>0.05892264334362111</v>
+        <v>0.0589210883931363</v>
       </c>
       <c r="I162" s="6" t="n">
         <v>48</v>
@@ -20898,7 +20983,7 @@
         <v>0.01</v>
       </c>
       <c r="O162" s="10" t="n">
-        <v>5.484225029207535</v>
+        <v>5.484080302191161</v>
       </c>
       <c r="P162" s="6" t="inlineStr">
         <is>
@@ -20922,7 +21007,7 @@
       </c>
       <c r="T162" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U162" s="6" t="inlineStr">
@@ -20956,13 +21041,13 @@
         </is>
       </c>
       <c r="F163" s="7" t="n">
-        <v>212384.6</v>
+        <v>212384.67</v>
       </c>
       <c r="G163" s="7" t="n">
         <v>3356.98</v>
       </c>
       <c r="H163" s="8" t="n">
-        <v>0.01580613660312471</v>
+        <v>0.01580613139356998</v>
       </c>
       <c r="I163" s="6" t="n">
         <v>18</v>
@@ -20983,7 +21068,7 @@
         <v>-0.9</v>
       </c>
       <c r="O163" s="10" t="n">
-        <v>4.903853881119441</v>
+        <v>4.903852264855085</v>
       </c>
       <c r="P163" s="6" t="inlineStr">
         <is>
@@ -21007,7 +21092,7 @@
       </c>
       <c r="T163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U163" s="6" t="inlineStr">
@@ -21092,7 +21177,7 @@
       </c>
       <c r="T164" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U164" s="6" t="inlineStr">
@@ -21177,7 +21262,7 @@
       </c>
       <c r="T165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U165" s="6" t="inlineStr">
@@ -21262,7 +21347,7 @@
       </c>
       <c r="T166" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U166" s="6" t="inlineStr">
@@ -21347,7 +21432,7 @@
       </c>
       <c r="T167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:58:02+00:00</t>
+          <t>2026-09-25T14:58:52+00:00</t>
         </is>
       </c>
       <c r="U167" s="6" t="inlineStr">

--- a/LP-Pair-Rankings.xlsx
+++ b/LP-Pair-Rankings.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -4201,7 +4201,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -4287,7 +4287,7 @@
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="T45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U45" s="6" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
@@ -4631,7 +4631,7 @@
       </c>
       <c r="T47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U47" s="6" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -5073,7 +5073,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -5687,7 +5687,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -6305,7 +6305,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -6395,7 +6395,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="T5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U5" s="6" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="T6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U6" s="6" t="inlineStr">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="T7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U7" s="6" t="inlineStr">
@@ -7017,7 +7017,7 @@
       </c>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="T9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U9" s="6" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="T10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U10" s="6" t="inlineStr">
@@ -7275,7 +7275,7 @@
       </c>
       <c r="T11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U11" s="6" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="T13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U13" s="6" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="T14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U14" s="6" t="inlineStr">
@@ -7619,7 +7619,7 @@
       </c>
       <c r="T15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U15" s="6" t="inlineStr">
@@ -7705,7 +7705,7 @@
       </c>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -7791,7 +7791,7 @@
       </c>
       <c r="T17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U17" s="6" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="T19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U19" s="6" t="inlineStr">
@@ -8049,7 +8049,7 @@
       </c>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
@@ -8135,7 +8135,7 @@
       </c>
       <c r="T21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U21" s="6" t="inlineStr">
@@ -8221,7 +8221,7 @@
       </c>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
@@ -8307,7 +8307,7 @@
       </c>
       <c r="T23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U23" s="6" t="inlineStr">
@@ -8393,7 +8393,7 @@
       </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
@@ -8479,7 +8479,7 @@
       </c>
       <c r="T25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U25" s="6" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U26" s="6" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="T27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U27" s="6" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="T29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U29" s="6" t="inlineStr">
@@ -8909,7 +8909,7 @@
       </c>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
@@ -8995,7 +8995,7 @@
       </c>
       <c r="T31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U31" s="6" t="inlineStr">
@@ -9081,7 +9081,7 @@
       </c>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="T33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U33" s="6" t="inlineStr">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
@@ -9339,7 +9339,7 @@
       </c>
       <c r="T35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U35" s="6" t="inlineStr">
@@ -9425,7 +9425,7 @@
       </c>
       <c r="T36" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U36" s="6" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U37" s="6" t="inlineStr">
@@ -9597,7 +9597,7 @@
       </c>
       <c r="T38" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U38" s="6" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="T39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U39" s="6" t="inlineStr">
@@ -9769,7 +9769,7 @@
       </c>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U41" s="6" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
@@ -10027,7 +10027,7 @@
       </c>
       <c r="T43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U43" s="6" t="inlineStr">
@@ -10113,7 +10113,7 @@
       </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="T45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U45" s="6" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="T46" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U46" s="6" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="T47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U47" s="6" t="inlineStr">
@@ -10457,7 +10457,7 @@
       </c>
       <c r="T48" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U48" s="6" t="inlineStr">
@@ -10543,7 +10543,7 @@
       </c>
       <c r="T49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U49" s="6" t="inlineStr">
@@ -10629,7 +10629,7 @@
       </c>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U50" s="6" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="T51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U51" s="6" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="T52" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U52" s="6" t="inlineStr">
@@ -10887,7 +10887,7 @@
       </c>
       <c r="T53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U53" s="6" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="T54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U54" s="6" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="T55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U55" s="6" t="inlineStr">
@@ -11145,7 +11145,7 @@
       </c>
       <c r="T56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U56" s="6" t="inlineStr">
@@ -11231,7 +11231,7 @@
       </c>
       <c r="T57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U57" s="6" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="T58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U58" s="6" t="inlineStr">
@@ -11403,7 +11403,7 @@
       </c>
       <c r="T59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U59" s="6" t="inlineStr">
@@ -11489,7 +11489,7 @@
       </c>
       <c r="T60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U60" s="6" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="T61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U61" s="6" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="T62" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U62" s="6" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="T63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U63" s="6" t="inlineStr">
@@ -11837,7 +11837,7 @@
       </c>
       <c r="T64" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U64" s="6" t="inlineStr">
@@ -11923,7 +11923,7 @@
       </c>
       <c r="T65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U65" s="6" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="T66" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U66" s="6" t="inlineStr">
@@ -12095,7 +12095,7 @@
       </c>
       <c r="T67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U67" s="6" t="inlineStr">
@@ -12181,7 +12181,7 @@
       </c>
       <c r="T68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U68" s="6" t="inlineStr">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="T69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U69" s="6" t="inlineStr">
@@ -12353,7 +12353,7 @@
       </c>
       <c r="T70" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U70" s="6" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="T71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U71" s="6" t="inlineStr">
@@ -12525,7 +12525,7 @@
       </c>
       <c r="T72" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U72" s="6" t="inlineStr">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="T73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U73" s="6" t="inlineStr">
@@ -12697,7 +12697,7 @@
       </c>
       <c r="T74" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U74" s="6" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="T75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U75" s="6" t="inlineStr">
@@ -12869,7 +12869,7 @@
       </c>
       <c r="T76" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U76" s="6" t="inlineStr">
@@ -12955,7 +12955,7 @@
       </c>
       <c r="T77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U77" s="6" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="T78" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U78" s="6" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="T79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U79" s="6" t="inlineStr">
@@ -13213,7 +13213,7 @@
       </c>
       <c r="T80" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U80" s="6" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="T81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U81" s="6" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="T82" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U82" s="6" t="inlineStr">
@@ -13471,7 +13471,7 @@
       </c>
       <c r="T83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U83" s="6" t="inlineStr">
@@ -13557,7 +13557,7 @@
       </c>
       <c r="T84" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U84" s="6" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="T85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U85" s="6" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="T86" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U86" s="6" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="T87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U87" s="6" t="inlineStr">
@@ -13901,7 +13901,7 @@
       </c>
       <c r="T88" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U88" s="6" t="inlineStr">
@@ -13987,7 +13987,7 @@
       </c>
       <c r="T89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U89" s="6" t="inlineStr">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="T90" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U90" s="6" t="inlineStr">
@@ -14159,7 +14159,7 @@
       </c>
       <c r="T91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U91" s="6" t="inlineStr">
@@ -14245,7 +14245,7 @@
       </c>
       <c r="T92" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U92" s="6" t="inlineStr">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="T93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U93" s="6" t="inlineStr">
@@ -14417,7 +14417,7 @@
       </c>
       <c r="T94" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U94" s="6" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="T95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U95" s="6" t="inlineStr">
@@ -14589,7 +14589,7 @@
       </c>
       <c r="T96" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U96" s="6" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="T97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U97" s="6" t="inlineStr">
@@ -14761,7 +14761,7 @@
       </c>
       <c r="T98" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U98" s="6" t="inlineStr">
@@ -14847,7 +14847,7 @@
       </c>
       <c r="T99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U99" s="6" t="inlineStr">
@@ -14933,7 +14933,7 @@
       </c>
       <c r="T100" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U100" s="6" t="inlineStr">
@@ -15019,7 +15019,7 @@
       </c>
       <c r="T101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U101" s="6" t="inlineStr">
@@ -15105,7 +15105,7 @@
       </c>
       <c r="T102" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U102" s="6" t="inlineStr">
@@ -15191,7 +15191,7 @@
       </c>
       <c r="T103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U103" s="6" t="inlineStr">
@@ -15277,7 +15277,7 @@
       </c>
       <c r="T104" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U104" s="6" t="inlineStr">
@@ -15363,7 +15363,7 @@
       </c>
       <c r="T105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U105" s="6" t="inlineStr">
@@ -15449,7 +15449,7 @@
       </c>
       <c r="T106" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U106" s="6" t="inlineStr">
@@ -15535,7 +15535,7 @@
       </c>
       <c r="T107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U107" s="6" t="inlineStr">
@@ -15621,7 +15621,7 @@
       </c>
       <c r="T108" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U108" s="6" t="inlineStr">
@@ -15707,7 +15707,7 @@
       </c>
       <c r="T109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U109" s="6" t="inlineStr">
@@ -15793,7 +15793,7 @@
       </c>
       <c r="T110" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U110" s="6" t="inlineStr">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="T111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U111" s="6" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="T112" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U112" s="6" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="T113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U113" s="6" t="inlineStr">
@@ -16137,7 +16137,7 @@
       </c>
       <c r="T114" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U114" s="6" t="inlineStr">
@@ -16223,7 +16223,7 @@
       </c>
       <c r="T115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U115" s="6" t="inlineStr">
@@ -16309,7 +16309,7 @@
       </c>
       <c r="T116" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U116" s="6" t="inlineStr">
@@ -16395,7 +16395,7 @@
       </c>
       <c r="T117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U117" s="6" t="inlineStr">
@@ -16481,7 +16481,7 @@
       </c>
       <c r="T118" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U118" s="6" t="inlineStr">
@@ -16567,7 +16567,7 @@
       </c>
       <c r="T119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U119" s="6" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="T120" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U120" s="6" t="inlineStr">
@@ -16739,7 +16739,7 @@
       </c>
       <c r="T121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U121" s="6" t="inlineStr">
@@ -16825,7 +16825,7 @@
       </c>
       <c r="T122" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U122" s="6" t="inlineStr">
@@ -16911,7 +16911,7 @@
       </c>
       <c r="T123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U123" s="6" t="inlineStr">
@@ -16997,7 +16997,7 @@
       </c>
       <c r="T124" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U124" s="6" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="T125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U125" s="6" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="T126" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U126" s="6" t="inlineStr">
@@ -17255,7 +17255,7 @@
       </c>
       <c r="T127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U127" s="6" t="inlineStr">
@@ -17341,7 +17341,7 @@
       </c>
       <c r="T128" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U128" s="6" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="T129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U129" s="6" t="inlineStr">
@@ -17513,7 +17513,7 @@
       </c>
       <c r="T130" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U130" s="6" t="inlineStr">
@@ -17599,7 +17599,7 @@
       </c>
       <c r="T131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U131" s="6" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="T132" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U132" s="6" t="inlineStr">
@@ -17775,7 +17775,7 @@
       </c>
       <c r="T133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U133" s="6" t="inlineStr">
@@ -17861,7 +17861,7 @@
       </c>
       <c r="T134" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U134" s="6" t="inlineStr">
@@ -17947,7 +17947,7 @@
       </c>
       <c r="T135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U135" s="6" t="inlineStr">
@@ -18033,7 +18033,7 @@
       </c>
       <c r="T136" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U136" s="6" t="inlineStr">
@@ -18123,7 +18123,7 @@
       </c>
       <c r="T137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U137" s="6" t="inlineStr">
@@ -18209,7 +18209,7 @@
       </c>
       <c r="T138" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U138" s="6" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="T139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U139" s="6" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="T140" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U140" s="6" t="inlineStr">
@@ -18467,7 +18467,7 @@
       </c>
       <c r="T141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U141" s="6" t="inlineStr">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="T142" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U142" s="6" t="inlineStr">
@@ -18639,7 +18639,7 @@
       </c>
       <c r="T143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U143" s="6" t="inlineStr">
@@ -18725,7 +18725,7 @@
       </c>
       <c r="T144" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U144" s="6" t="inlineStr">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="T145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U145" s="6" t="inlineStr">
@@ -18897,7 +18897,7 @@
       </c>
       <c r="T146" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U146" s="6" t="inlineStr">
@@ -18983,7 +18983,7 @@
       </c>
       <c r="T147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U147" s="6" t="inlineStr">
@@ -19069,7 +19069,7 @@
       </c>
       <c r="T148" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U148" s="6" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="T149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U149" s="6" t="inlineStr">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="T150" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U150" s="6" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="T151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U151" s="6" t="inlineStr">
@@ -19413,7 +19413,7 @@
       </c>
       <c r="T152" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U152" s="6" t="inlineStr">
@@ -19499,7 +19499,7 @@
       </c>
       <c r="T153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U153" s="6" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="T154" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U154" s="6" t="inlineStr">
@@ -19671,7 +19671,7 @@
       </c>
       <c r="T155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U155" s="6" t="inlineStr">
@@ -19757,7 +19757,7 @@
       </c>
       <c r="T156" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U156" s="6" t="inlineStr">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="T157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U157" s="6" t="inlineStr">
@@ -19929,7 +19929,7 @@
       </c>
       <c r="T158" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U158" s="6" t="inlineStr">
@@ -20015,7 +20015,7 @@
       </c>
       <c r="T159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U159" s="6" t="inlineStr">
@@ -20101,7 +20101,7 @@
       </c>
       <c r="T160" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U160" s="6" t="inlineStr">
@@ -20187,7 +20187,7 @@
       </c>
       <c r="T161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U161" s="6" t="inlineStr">
@@ -20273,7 +20273,7 @@
       </c>
       <c r="T162" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U162" s="6" t="inlineStr">
@@ -20359,7 +20359,7 @@
       </c>
       <c r="T163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U163" s="6" t="inlineStr">
@@ -20445,7 +20445,7 @@
       </c>
       <c r="T164" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U164" s="6" t="inlineStr">
@@ -20535,7 +20535,7 @@
       </c>
       <c r="T165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U165" s="6" t="inlineStr">
@@ -20621,7 +20621,7 @@
       </c>
       <c r="T166" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U166" s="6" t="inlineStr">
@@ -20707,7 +20707,7 @@
       </c>
       <c r="T167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-25T15:22:42+00:00</t>
+          <t>2026-09-25T15:23:08+00:00</t>
         </is>
       </c>
       <c r="U167" s="6" t="inlineStr">
